--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0022.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0022.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>&lt;color=#f0c154&gt;Mất HP khi vào Memory Zone.&lt;/color&gt;</t>
+          <t>&lt;color=#f0c154&gt;Mất HP khi bước vào Vùng Ký Ức.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>&lt;color=#f0c154&gt;Giảm mạnh HP Tối Đa, nhưng sẽ không bị hạ gục ở cấp Symphony cao.&lt;/color&gt;</t>
+          <t>&lt;color=#f0c154&gt;Giảm mạnh HP tối đa, nhưng sẽ không bị hạ gục ở Cấp Độ Giao Hưởng cao.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>&lt;color=#f0c154&gt;Tăng DMG Dodge Counter ở cấp Symphony cao.&lt;/color&gt;</t>
+          <t>&lt;color=#f0c154&gt;Tăng Sát Thương Né Phản Đòn ở Cấp Độ Giao Hưởng cao.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>&lt;color=#f0c154&gt;Dodge Counter giảm Cooldown Kỹ Năng ở cấp Symphony cao.&lt;/color&gt;</t>
+          <t>&lt;color=#f0c154&gt;Né Phản Đòn giảm Thời gian hồi chiêu Kỹ năng ở Cấp Độ Giao Hưởng cao.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>&lt;color=#f0c154&gt;Tăng Crit. Rate và Crit. DMG ở cấp Symphony cao.&lt;/color&gt;</t>
+          <t>&lt;color=#f0c154&gt;Tăng Crit. Rate và Crit. DMG ở Cấp Độ Giao Hưởng cao.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Càng thu thập nhiều &lt;color=Highlight&gt;Attribute Orbs&lt;/color&gt;, ngươi gây sát thương càng cao.</t>
+          <t>Càng thu thập nhiều &lt;color=Highlight&gt;Attribute Orb&lt;/color&gt;, ngươi gây DMG càng cao.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Càng thu thập nhiều &lt;color=Highlight&gt;Metaphors&lt;/color&gt;, ngươi gây và nhận sát thương càng cao.</t>
+          <t>Càng thu thập nhiều &lt;color=Highlight&gt;Metaphor&lt;/color&gt;, ngươi gây và nhận DMG càng cao.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Cấp Độ Chuỗi Resonance của tất cả thành viên trong đội được tăng thêm {0}.</t>
+          <t>Cấp Độ Resonance Chain của tất cả thành viên trong đội được tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt nhận hiệu ứng DMG Amplification, &lt;color=#b94f4e&gt;but their HP is capped at {1} of their Max HP&lt;/color&gt;.</t>
+          <t>Resonator đang kích hoạt nhận hiệu ứng Khuếch Đại Sát Thương, &lt;color=#b94f4e&gt;nhưng HP tối đa của họ bị giới hạn ở {1} HP tối đa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Resonator hiện tại phục hồi HP khi gây sát thương và gây nhiều sát thương hơn khi HP thấp. &lt;color=#b94f4e&gt;Casting skills now consumes HP&lt;/color&gt;.</t>
+          <t>Resonator hiện tại phục hồi HP khi gây DMG và gây nhiều DMG hơn khi HP thấp. &lt;color=#b94f4e&gt;Kỹ năng thi triển giờ đây tiêu hao HP&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt gây thêm sát thương khi bước vào Khu Vực Ký Ức mới trong một khoảng thời gian. &lt;color=#b94f4e&gt;Later, they take more DMG.&lt;/color&gt;</t>
+          <t>Resonator đang kích hoạt gây thêm DMG khi bước vào Khu Vực Ký Ức mới trong một khoảng thời gian. &lt;color=#b94f4e&gt;Sau đó, họ sẽ chịu nhiều DMG hơn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt được tăng tất cả kỹ năng lên cấp tối đa và Cooldown chiêu của một số kỹ năng cụ thể được giảm. &lt;color=#b94f4e&gt;However, their Resonance Liberation is disabled&lt;/color&gt;.</t>
+          <t>Resonator đang kích hoạt được tăng tất cả kỹ năng lên cấp tối đa và Cooldown chiêu của một số kỹ năng cụ thể được giảm. &lt;color=#b94f4e&gt;Tuy nhiên, Resonance Liberation của họ bị vô hiệu hóa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Dodging&lt;/color&gt; gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên kẻ địch xung quanh.</t>
+          <t>&lt;color=Highlight&gt;Né Tránh&lt;/color&gt; gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; lên kẻ địch xung quanh.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Sát thương gây ra bởi &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được tăng cường, &lt;color=#b94f4e&gt;but costs STA.&lt;/color&gt;</t>
+          <t>Sát thương gây ra bởi &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được tăng cường, &lt;color=#b94f4e&gt;nhưng tiêu tốn STA.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt có Cooldown chiêu của một số kỹ năng được đặt lại ngay lập tức khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;. Ngoài ra, các đòn tấn công của họ hồi phục HP và họ chịu ít sát thương hơn.</t>
+          <t>Resonator đang kích hoạt có Cooldown chiêu của một số kỹ năng được đặt lại ngay lập tức khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;. Ngoài ra, các đòn tấn công của họ hồi phục HP và họ chịu ít DMG hơn.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Mỗi {0} giây, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên kẻ địch xung quanh và áp dụng &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; cùng &lt;color=Highlight&gt;Aero Erosion&lt;/color&gt; lên chúng.</t>
+          <t>Mỗi {0} giây, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; lên kẻ địch xung quanh và áp dụng &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; cùng &lt;color=Highlight&gt;Aero Erosion&lt;/color&gt; lên chúng.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Thực hiện &lt;color=Highlight&gt;Tune Break Skill&lt;/color&gt; sẽ khuếch đại sát thương gây ra và miễn nhiễm với &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần sát thương tiếp theo P=lần sát thương tiếp theo SapTag=1} sau đây.</t>
+          <t>Thực hiện &lt;color=Highlight&gt;Kỹ Năng Phá Nhịp&lt;/color&gt; sẽ khuếch đại DMG gây ra và miễn nhiễm với &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần DMG tiếp theo P=lần DMG tiếp theo SapTag=1} sau đây.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Hồi phục kích hoạt tia laser gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Hồi phục kích hoạt tia laser gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Khi ở trên không, tất cả thành viên trong đội hồi phục STA nhanh hơn và gây nhiều sát thương hơn.</t>
+          <t>Khi ở trên không, tất cả thành viên trong đội hồi phục STA nhanh hơn và gây nhiều DMG hơn.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Concerto Skill&lt;/color&gt; sẽ tăng Tỷ Lệ Tích Lũy Off-Tune của Resonator đang hoạt động.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Kỹ Năng Concerto&lt;/color&gt; sẽ tăng Tỷ Lệ Tích Lũy Off-Tune của Resonator đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Cứ {2} đòn Basic Attack trúng đích sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; bắn Bom Bay, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Cứ {2} đòn Basic Attack trúng đích sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; bắn Bom Bay, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Mỗi {2} đòn Heavy Attack sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; bắn Liên Tục Phi Tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Mỗi {2} đòn Heavy Attack sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; bắn Liên Tục Phi Tiêu, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trúng đích sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; thi triển Hand of Corruption, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trúng đích sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; thi triển Hand of Corruption, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; bắn Pháo Pheromone, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt; triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; bắn Pháo Pheromone, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Concerto Skill&lt;/color&gt; triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; để hồi HP và tăng Sát Thương.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Kỹ Năng Concerto&lt;/color&gt; triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; để hồi HP và tăng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Tune Break Skill&lt;/color&gt;, triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; tấn công tất cả kẻ địch gần đó bằng Thánh Lửa, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi sử dụng &lt;color=Highlight&gt;Kỹ Năng Phá Nhịp&lt;/color&gt;, triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; tấn công tất cả kẻ địch gần đó bằng Thánh Lửa, gây &lt;color=Fire&gt;DMG Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Trong chiến đấu, triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; mỗi {0} giây để phục hồi HP và tạo Shield.</t>
+          <t>Trong chiến đấu, triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; mỗi {0} giây để phục hồi HP và tạo Khiên.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Resonator hiện tại phục hồi Concerto Energy và Resonance Energy mỗi giây. Đồng thời, Cooldown chiêu của &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; và &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; cũng được rút ngắn.</t>
+          <t>Resonator hiện tại phục hồi Năng Lượng Giao Hưởng và Resonance Energy mỗi giây. Đồng thời, Cooldown chiêu của &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; và &lt;color=Highlight&gt;Kỹ Năng Vọng Âm&lt;/color&gt; cũng được rút ngắn.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;Attribute {Cus:Sap,S=Orb P=Orbs SapTag=0}&lt;/color&gt; nhận được sẽ tăng {1} sát thương gây ra.</t>
+          <t>Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;Thuộc Tính {Cus:Sap,S=Orb P=Orbs SapTag=0}&lt;/color&gt; nhận được sẽ tăng {1} DMG gây ra.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Metaphor P=Metaphors SapTag=0}&lt;/color&gt; nhận được sẽ tăng {1} sát thương gây ra và {2} sát thương nhận vào.</t>
+          <t>Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Ẩn Dụ P=Ẩn Dụ SapTag=0}&lt;/color&gt; nhận được sẽ tăng {1} DMG gây ra và {2} DMG nhận vào.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Cấp Độ Chuỗi Resonance của tất cả thành viên trong đội được tăng thêm {0}.</t>
+          <t>Cấp Độ Resonance Chain của tất cả thành viên trong đội được tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt nhận {0} DMG Amplification, &lt;color=#b94f4e&gt;but their HP is capped at {1} of their Max HP&lt;/color&gt;.</t>
+          <t>Resonator đang kích hoạt nhận {0} Khuếch Đại Sát Thương, &lt;color=#b94f4e&gt;nhưng HP tối đa của họ bị giới hạn ở {1} HP tối đa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt hồi phục HP bằng {0} lượng HP đã mất khi gây sát thương, kích hoạt mỗi 1 giây. Cứ mỗi {1} HP mất đi, sát thương gây ra được Khuếch Đại thêm {2}. &lt;color=#b94f4e&gt;Casting Resonance Skill or Resonance Liberation consumes {3} of their current HP&lt;/color&gt;.</t>
+          <t>Resonator đang kích hoạt hồi phục HP bằng {0} lượng HP đã mất khi gây DMG, kích hoạt mỗi 1 giây. Cứ mỗi {1} HP mất đi, DMG gây ra được Khuếch Đại thêm {2}. &lt;color=#b94f4e&gt;Sử dụng Resonance Skill hoặc Resonance Liberation sẽ tiêu hao {3} HP hiện tại&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt nhận {1} DMG Amplification trong {0} giây khi bước vào Khu Vực Ký Ức mới. &lt;color=#b94f4e&gt;Sau khi {2}s, the DMG they take is additionally Amplified by {3}&lt;/color&gt;.</t>
+          <t>Resonator đang kích hoạt nhận {1} Khuếch Đại Sát Thương trong {0} giây khi bước vào Khu Vực Ký Ức mới. &lt;color=#b94f4e&gt;Sau {2} giây, DMG họ nhận thêm bị Khuếch Đại thêm {3}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt được tăng tất cả kỹ năng lên cấp {0}, và Cooldown chiêu của &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; giảm {1}. &lt;color=#b94f4e&gt;However, their Resonance Liberation is disabled&lt;/color&gt;.</t>
+          <t>Resonator đang kích hoạt được tăng tất cả kỹ năng lên cấp {0}, và Cooldown chiêu của &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; giảm {1}. &lt;color=#b94f4e&gt;Tuy nhiên, Resonance Liberation của họ bị vô hiệu hóa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Dodging&lt;/color&gt; gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; bằng {0} Tấn Công lên kẻ địch xung quanh.</t>
+          <t>&lt;color=Highlight&gt;Né Tránh&lt;/color&gt; gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; bằng {0} ATK lên kẻ địch xung quanh.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Sát thương gây ra bởi &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; tăng thêm {1}, &lt;color=#b94f4e&gt;but additionally consumes {0} points of STA&lt;/color&gt;.</t>
+          <t>Sát thương gây ra bởi &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; tăng thêm {1}, &lt;color=#b94f4e&gt;nhưng tiêu hao thêm {0} điểm STA&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3436,9 +3436,9 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt có Cooldown chiêu của &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được đặt lại ngay lập tức khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;. Ngoài ra, họ nhận &lt;color=Highlight&gt;Murmuring Heal&lt;/color&gt; và &lt;color=Highlight&gt;Dream Veil&lt;/color&gt; trong {0} giây.
-&lt;color=Highlight&gt;Murmuring Heal&lt;/color&gt;: Gây sát thương sẽ hồi phục HP bằng {1} HP tối đa, kích hoạt mỗi 1 giây.
-&lt;color=Highlight&gt;Dream Veil&lt;/color&gt;: Sát thương nhận vào giảm {2}. Hiệu ứng này giảm {4} sau mỗi {3} giây.</t>
+          <t>Resonator đang kích hoạt có Cooldown chiêu của &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được đặt lại ngay lập tức khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;. Ngoài ra, họ nhận &lt;color=Highlight&gt;Hồi Phục Thầm Lặng&lt;/color&gt; và &lt;color=Highlight&gt;Màn Mộng Ảo&lt;/color&gt; trong {0} giây.
+&lt;color=Highlight&gt;Hồi Phục Thầm Lặng&lt;/color&gt;: Gây sát thương sẽ hồi phục HP bằng {1} HP tối đa, kích hoạt mỗi 1 giây.
+&lt;color=Highlight&gt;Màn Mộng Ảo&lt;/color&gt;: Sát thương nhận vào giảm {2}. Hiệu ứng này giảm {4} sau mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Mỗi {0} giây, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; bằng {1} Tấn Công lên kẻ địch xung quanh và áp dụng &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=2} &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; cùng &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=3} &lt;color=Highlight&gt;Aero Erosion&lt;/color&gt; lên chúng.</t>
+          <t>Mỗi {0} giây, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; bằng {1} ATK lên kẻ địch xung quanh và áp dụng &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=2} &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; cùng &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=3} &lt;color=Highlight&gt;Aero Erosion&lt;/color&gt; lên chúng.</t>
         </is>
       </c>
     </row>
@@ -3569,8 +3569,8 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Tune Break Skill&lt;/color&gt;, khuếch đại sát thương gây ra thêm {0} và nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} &lt;color=Highlight&gt;Ichor's Shelter&lt;/color&gt; trong {2} giây.
-&lt;color=Highlight&gt;Ichor's Shelter&lt;/color&gt;: Khi nhận sát thương, tiêu hao &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=3} để miễn nhiễm sát thương trong {4} giây.</t>
+          <t>Khi sử dụng &lt;color=Highlight&gt;Kỹ Năng Phá Nhịp&lt;/color&gt;, khuếch đại DMG gây ra thêm {0} và nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} &lt;color=Highlight&gt;Lá Chắn Ichor&lt;/color&gt; trong {2} giây.
+&lt;color=Highlight&gt;Lá Chắn Ichor&lt;/color&gt;: Khi nhận DMG, tiêu hao &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=3} để miễn nhiễm DMG trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Hồi máu kích hoạt {0} tia laser, mỗi tia gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; tương đương {1} HP tối đa, kích hoạt mỗi {2} giây.</t>
+          <t>Hồi máu kích hoạt {0} tia laser, mỗi tia gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; tương đương {1} HP tối đa, kích hoạt mỗi {2} giây.</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Khi ở trên không, tốc độ hồi phục STA của tất cả thành viên trong đội tăng thêm {0} và sát thương được khuếch đại thêm {1}.</t>
+          <t>Khi ở trên không, tốc độ hồi phục STA của tất cả thành viên trong đội tăng thêm {0} và DMG được khuếch đại thêm {1}.</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Khi kẻ địch gần đó chịu Sát Thương từ Trạng Thái Tiêu Cực, sẽ giảm ngay Cooldown chiêu của &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; đi {0} giây và hồi {1} điểm &lt;color=Highlight&gt;Resonance Energy&lt;/color&gt;. Hiệu ứng này kích hoạt mỗi giây một lần.</t>
+          <t>Khi kẻ địch gần đó chịu Sát Thương từ Trạng Thái Tiêu Cực, sẽ giảm ngay Thời gian hồi chiêu của &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; đi {0} giây và hồi {1} điểm &lt;color=Highlight&gt;Resonance Energy&lt;/color&gt;. Hiệu ứng này kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Concerto Skill&lt;/color&gt; sẽ tăng Tỷ Lệ Tích Lũy Off-Tune của Resonator đang hoạt động lên {0} trong {1} giây.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Kỹ Năng Concerto&lt;/color&gt; sẽ tăng Tỷ Lệ Tích Lũy Off-Tune của Resonator đang hoạt động lên {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=Highlight&gt;{2}&lt;/color&gt; đòn Basic Attack trúng đích sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; phóng {0} Quả Bom Bay, mỗi quả gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; bằng {1} Attack.</t>
+          <t>Mỗi &lt;color=Highlight&gt;{2}&lt;/color&gt; đòn Đòn Basic Attack trúng đích sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; phóng {0} Quả Bom Bay, mỗi quả gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; bằng {1} ATK.</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=Highlight&gt;{2}&lt;/color&gt; đòn Heavy Attack trúng đích sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; phóng {0} Quả Bom Bay Xếp Chồng, mỗi quả gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; bằng {1} Attack.</t>
+          <t>Mỗi &lt;color=Highlight&gt;{2}&lt;/color&gt; đòn Đòn Heavy Attack trúng đích sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; phóng {0} Quả Bom Bay Xếp Chồng, mỗi quả gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; bằng {1} ATK.</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trúng đích sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; thi triển Hand of Corruption {2} lần, mỗi lần gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; bằng {0} Tấn Công. Hiệu ứng này chỉ kích hoạt mỗi {1} giây.</t>
+          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trúng đích sẽ triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; thi triển Hand of Corruption {2} lần, mỗi lần gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; bằng {0} ATK. Hiệu ứng này chỉ kích hoạt mỗi {1} giây.</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; bắn {0} Pháo Pheromone, mỗi phát gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; bằng {1} Tấn Công. Hiệu ứng này kích hoạt mỗi {2} giây một lần.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt; triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; bắn {0} Pháo Pheromone, mỗi phát gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; bằng {1} ATK. Hiệu ứng này kích hoạt mỗi {2} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Concerto Skill&lt;/color&gt; triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; để hồi HP bằng {0} HP tối đa và khuếch đại Sát Thương gây ra thêm {1} trong {2} giây. Hiệu ứng này kích hoạt mỗi {3} giây một lần.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Kỹ Năng Concerto&lt;/color&gt; triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; để hồi HP bằng {0} HP tối đa và khuếch đại Sát Thương gây ra thêm {1} trong {2} giây. Hiệu ứng này kích hoạt mỗi {3} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Tune Break Skill&lt;/color&gt;, triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; tấn công tất cả kẻ địch gần đó bằng Thánh Lửa, mỗi đòn gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; bằng {0} Tấn Công. Hiệu ứng này kích hoạt mỗi {1} giây một lần.</t>
+          <t>Khi sử dụng &lt;color=Highlight&gt;Kỹ Năng Phá Nhịp&lt;/color&gt;, triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; tấn công tất cả kẻ địch gần đó bằng Thánh Lửa, mỗi đòn gây &lt;color=Fire&gt;DMG Fusion&lt;/color&gt; bằng {0} ATK. Hiệu ứng này kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Trong chiến đấu, triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; mỗi {0} giây để phục hồi HP bằng {1}% HP tối đa và tạo Shield với số điểm tương đương.</t>
+          <t>Trong chiến đấu, triệu hồi &lt;color=Highlight&gt;Namipon&lt;/color&gt; mỗi {0} giây để phục hồi HP bằng {1}% HP tối đa và tạo Khiên với số điểm tương đương.</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Resonator hiện tại phục hồi {1} điểm Concerto Energy và Resonance Energy mỗi giây. Đồng thời, Cooldown chiêu của &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; và &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; được rút ngắn {0}.</t>
+          <t>Resonator hiện tại phục hồi {1} điểm Năng Lượng Giao Hưởng và Resonance Energy mỗi giây. Đồng thời, Cooldown chiêu của &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; và &lt;color=Highlight&gt;Kỹ Năng Vọng Âm&lt;/color&gt; được rút ngắn {0}.</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>ATK is increased by {0}</t>
+          <t>ATK tăng {0}</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Dodge thành công phục hồi {0} HP tối đa. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Né tránh thành công phục hồi {0} HP tối đa. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Increase lượng Dream Fragment nhận được thêm {0}.</t>
+          <t>Tăng lượng Dream Fragment nhận được thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>HP tăng thêm {0}.</t>
+          <t>Tăng HP thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>DMG tăng thêm {0}.</t>
+          <t>Tấn Công tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Increase lượng Dream Fragment nhận được thêm {0}.</t>
+          <t>Tăng lượng Dream Fragment nhận được thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Dodge thành công hồi {0} Thể Lực.</t>
+          <t>Né tránh thành công hồi {0} STA.</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Khi bước vào Khu Vực Ký Ức, miễn nhiễm với sát thương từ đòn tấn công đầu tiên trong vòng {0} giây.</t>
+          <t>Khi bước vào Khu Vực Ký Ức, miễn nhiễm với DMG từ đòn tấn công đầu tiên trong vòng {0} giây.</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>ATK tăng thêm {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>HP tăng thêm {0}.</t>
+          <t>Tăng HP thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>DMG tăng thêm {0}.</t>
+          <t>Tấn Công tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Skip the turn&lt;/color&gt; và &lt;color=Highlight&gt;act last next round&lt;/color&gt; khi ở đầu ngăn xếp.</t>
+          <t>Bỏ lượt hiện tại và &lt;color=Highlight&gt;hành động cuối cùng ở vòng tiếp theo&lt;/color&gt; khi đứng đầu một chồng.</t>
         </is>
       </c>
     </row>
@@ -5983,13 +5983,13 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>Về sự kiện
-Những bài test tiêu chuẩn khiến cậu chán ngấy, nhưng một bài test kỹ năng chiến đấu lại khiến máu chiến của cậu sôi sục! Vậy thì hãy thể hiện hết mình và bước vào cuộc đọ sức trong Bài Kiểm Tra Kỹ Năng Combat của Huấn luyện viên B.1.N.G.O.!
+Những bài kiểm tra tiêu chuẩn khiến cậu chán ngấy, nhưng một bài kiểm tra kỹ năng chiến đấu lại khiến máu chiến của cậu sôi sục! Vậy thì hãy thể hiện hết mình và bước vào cuộc đọ sức trong Bài Kiểm Tra Kỹ Năng Chiến Đấu của Huấn luyện viên B.1.N.G.O.!
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và kích hoạt Nexus Resonance Startorch Academy trong Nhiệm vụ Main "Ngọn Lửa Dưới Băng Nguyên".
+Đạt Cấp Liên Minh 14 và kích hoạt Nexus Cộng Hưởng Học viện Startorch trong Nhiệm vụ Chính "Ngọn Lửa Dưới Băng Nguyên".
 Quy tắc
-Sự kiện gồm 7 bộ bài test. Mỗi bộ bao gồm Preliminary với các Giám khảo Phụ và Vòng Chung Kết với Giám khảo Main.
-Đáp ứng các yêu cầu khác nhau để tăng sức mạnh cho đội trong Preliminary.
-Tất cả các buff nhận được trong Preliminary sẽ được giữ nguyên trong Vòng Chung Kết, nơi chỉ còn một mục tiêu duy nhất—hạ gục càng nhiều HP của Giám khảo Main càng tốt để ghi điểm cao!</t>
+Sự kiện gồm 7 bộ bài kiểm tra. Mỗi bộ bao gồm Vòng Sơ Loại với các Giám khảo Phụ và Vòng Chung Kết với Giám khảo Chính.
+Đáp ứng các yêu cầu khác nhau để tăng sức mạnh cho đội trong Vòng Sơ Loại.
+Tất cả các buff nhận được trong Vòng Sơ Loại sẽ được giữ nguyên trong Vòng Chung Kết, nơi chỉ còn một mục tiêu duy nhất—hạ gục càng nhiều HP của Giám khảo Chính càng tốt để ghi điểm cao!</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Preview Hiệu ứng</t>
+          <t>Xem trước Hiệu ứng</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Tiêu diệt Assessor có khả năng ban &lt;color=#ffb04a&gt;status buff&lt;/color&gt;.</t>
+          <t>Tiêu diệt Assessor có khả năng ban &lt;color=#ffb04a&gt;hiệu ứng trạng thái tăng cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>HP của Chief Assessor x999</t>
+          <t>HP Người Giám Định Trưởng x999</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Buff Nâng Cao</t>
+          <t>Hiệu Ứng Tiến Hóa</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Buff Common</t>
+          <t>Tăng Cường Thường</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Chưa nhận được buff nào</t>
+          <t>Chưa nhận được hiệu ứng tăng cường nào</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được phục hồi về 100%.</t>
+          <t>Khi bắt đầu thử thách, &lt;color=#ffb04a&gt;Năng Lượng Giao Hưởng&lt;/color&gt; được phục hồi về 100%.</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Khi thử thách bắt đầu, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được hồi phục về 100%. Nhận Core Resonance: &lt;color=#ffb04a&gt;Resonance Liberation DMG&lt;/color&gt; tăng 20% và &lt;color=#ffb04a&gt;Energy Regen&lt;/color&gt; tăng 30%.</t>
+          <t>Khi thử thách bắt đầu, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được hồi phục về 100%. Nhận Lõi Cộng Hưởng: &lt;color=#ffb04a&gt;Sát Thương Resonance Liberation&lt;/color&gt; tăng 20% và &lt;color=#ffb04a&gt;Hồi Phục Năng Lượng&lt;/color&gt; tăng 30%.</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Khi thử thách bắt đầu, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được hồi phục về 100%. Nhận Core Lệch Nhịp: &lt;color=#ffb04a&gt;Off-Tune Level Buildup Rate&lt;/color&gt; tăng 30%, &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; tăng 300%, và &lt;color=#ffb04a&gt;Tune Break Boost&lt;/color&gt; tăng 30.</t>
+          <t>Khi thử thách bắt đầu, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được hồi phục về 100%. Nhận Lõi Lệch Nhịp: &lt;color=#ffb04a&gt;Tốc Độ Tích Lũy Cấp Độ Lệch Nhịp&lt;/color&gt; tăng 30%, &lt;color=#ffb04a&gt;Sát Thương Phá Nhịp&lt;/color&gt; tăng 300%, và &lt;color=#ffb04a&gt;Hiệu Ứng Tăng Cường Phá Nhịp&lt;/color&gt; tăng 30.</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Khi thử thách bắt đầu, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được hồi phục về 100%. Nhận Core Méo Nhịp: Khi Resonators trong đội có thể phản ứng với &lt;color=#ffb04a&gt;Tune Strain - Interfered&lt;/color&gt; gây sát thương lên mục tiêu bị ảnh hưởng bởi &lt;color=#ffb04a&gt;Tune Strain - Interfered&lt;/color&gt;, mục tiêu sẽ được tính thêm 1 tầng &lt;color=#ffb04a&gt;Tune Strain - Interfered&lt;/color&gt;. Hiệu ứng này không bị giới hạn số tầng. &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; tăng 200%.</t>
+          <t>Khi thử thách bắt đầu, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được hồi phục về 100%. Nhận Lõi Méo Nhịp: Khi Resonator trong đội có thể phản ứng với &lt;color=#ffb04a&gt;Méo Nhịp - Nhiễu Loạn&lt;/color&gt; gây DMG lên mục tiêu bị ảnh hưởng bởi &lt;color=#ffb04a&gt;Méo Nhịp - Nhiễu Loạn&lt;/color&gt;, mục tiêu sẽ được tính thêm 1 tầng &lt;color=#ffb04a&gt;Méo Nhịp - Nhiễu Loạn&lt;/color&gt;. Hiệu ứng này không bị giới hạn số tầng. &lt;color=#ffb04a&gt;Sát Thương Phá Nhịp&lt;/color&gt; tăng 200%.</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Khi thử thách bắt đầu, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được hồi phục về 100%. Nhận Core Vỡ Nhịp: &lt;color=#ffb04a&gt;Tune Rupture DMG&lt;/color&gt; tăng 100%. &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; tăng 200%, và &lt;color=#ffb04a&gt;Tune Break Boost&lt;/color&gt; tăng 40.</t>
+          <t>Khi thử thách bắt đầu, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được hồi phục về 100%. Nhận Lõi Vỡ Nhịp: &lt;color=#ffb04a&gt;Sát Thương Vỡ Nhịp&lt;/color&gt; tăng 100%. &lt;color=#ffb04a&gt;Sát Thương Phá Nhịp&lt;/color&gt; tăng 200%, và &lt;color=#ffb04a&gt;Hiệu Ứng Tăng Cường Phá Nhịp&lt;/color&gt; tăng 40.</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được phục hồi về 100%. Nhận Core Echoes: Sử dụng Kỹ Năng Echoes làm tăng &lt;color=#ffb04a&gt;Echo Skill DMG&lt;/color&gt; thêm 4%, tối đa 5 lớp. Các Echoes cùng tên chỉ có thể kích hoạt hiệu ứng này một lần.</t>
+          <t>Khi bắt đầu thử thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được phục hồi về 100%. Nhận Lõi Echo: Sử dụng Kỹ Năng Echo làm tăng &lt;color=#ffb04a&gt;Sát Thương Kỹ Năng Echo&lt;/color&gt; thêm 4%, tối đa 5 lớp. Các Echo cùng tên chỉ có thể kích hoạt hiệu ứng này một lần.</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được phục hồi về 100%. Nhận Core Glacio Chafe: Gây ra &lt;color=#ffb04a&gt;Glacio Chafe&lt;/color&gt; làm tăng &lt;color=#ffb04a&gt;Glacio DMG&lt;/color&gt; thêm 10% trong 30 giây, tối đa 3 lớp.</t>
+          <t>Khi bắt đầu thử thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được phục hồi về 100%. Nhận Lõi Glacio Chafe: Gây ra &lt;color=#ffb04a&gt;Glacio Chafe&lt;/color&gt; làm tăng &lt;color=#ffb04a&gt;Sát Thương Glacio&lt;/color&gt; thêm 10% trong 30 giây, tối đa 3 lớp.</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được phục hồi 100%. Nhận &lt;color=#ffb04a&gt;Fusion Burst Core&lt;/color&gt;: Gây &lt;color=#ffb04a&gt;Fusion Burst&lt;/color&gt; làm tăng &lt;color=#ffb04a&gt;Fusion DMG&lt;/color&gt; thêm 10% trong 30 giây, cộng dồn tối đa 3 lần.</t>
+          <t>Khi bắt đầu thử thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được phục hồi về 100%. Nhận Lõi Fusion Burst: Gây ra &lt;color=#ffb04a&gt;Fusion Burst&lt;/color&gt; làm tăng &lt;color=#ffb04a&gt;Sát Thương Fusion&lt;/color&gt; thêm 10% trong 30 giây, tối đa 3 lớp.</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Khi tham gia thử thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được hồi phục về 100%. Khi đồng hồ thi đấu còn &lt;color=#ffb04a&gt;less than 60s&lt;/color&gt;, Giai Đoạn Quyết Chiến sẽ kích hoạt, &lt;color=#ffb04a&gt;increasing Total DMG by 60%&lt;/color&gt;.</t>
+          <t>Khi tham gia thử thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được hồi phục về 100%. Khi đồng hồ thi đấu còn &lt;color=#ffb04a&gt;dưới 60 giây&lt;/color&gt;, Giai Đoạn Quyết Chiến sẽ kích hoạt, &lt;color=#ffb04a&gt;tăng Tổng Sát Thương lên 60%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Tấn Công tăng &lt;color=#ffb04a&gt;{0}&lt;/color&gt; (có thể cộng dồn).</t>
+          <t>ATK tăng &lt;color=#ffb04a&gt;{0}&lt;/color&gt; (có thể cộng dồn).</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Nhận &lt;color=#ffb04a&gt;{0}&lt;/color&gt; DMG Amplification Toàn Bộ Thuộc Tính (có thể chồng chất).</t>
+          <t>Nhận &lt;color=#ffb04a&gt;{0}&lt;/color&gt; Khuếch Đại Sát Thương Toàn Bộ Thuộc Tính (có thể chồng chất).</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Mảnh Tỉ Lệ Bạo Kích</t>
+          <t>Mảnh Tăng Crit. Rate</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Mảnh Sát Thương Bạo Kích</t>
+          <t>Mảnh Crit. DMG</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Mảnh DMG I</t>
+          <t>Mảnh Sát Thương I</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Mảnh DMG II</t>
+          <t>Mảnh Sát Thương II</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Sát thương Resonance Liberation tăng {0}. Hồi phục Năng Lượng tăng {1}.</t>
+          <t>DMG Resonance Liberation tăng {0}. Hồi phục Năng Lượng tăng {1}.</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Tốc Độ Tích Lũy Mistune tăng thêm {0}. Sát thương Tune Break tăng thêm {1}. Hiệu ứng Tune Break tăng thêm {2}.</t>
+          <t>Tốc Độ Tích Lũy Lệch Tần tăng thêm {0}. DMG Phá Tần tăng thêm {1}. Hiệu ứng Phá Tần tăng thêm {2}.</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Gây sát thương lên mục tiêu bị Tune Strain - Interfered sẽ tăng thêm {0} tầng Tune Strain - Interfered cho chúng. Hiệu ứng này không bị giới hạn số tầng. Sát thương Phá Nhịp tăng thêm {1}.</t>
+          <t>Gây DMG lên mục tiêu bị Tune Strain - Interfered sẽ tăng thêm {0} tầng Tune Strain - Interfered cho chúng. Hiệu ứng này không bị giới hạn số tầng. DMG Phá Nhịp tăng thêm {1}.</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Sát thương Tune Rupture tăng {0}. Sát thương Tune Break tăng {1}. Hiệu ứng Tune Break Boost tăng {2}.</t>
+          <t>DMG Tune Rupture tăng {0}. DMG Tune Break tăng {1}. Hiệu ứng Tune Break Boost tăng {2}.</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Echoes sẽ tăng Sát Thương Kỹ Năng Echoes thêm {0}, tối đa {1} tầng. Các Echoes cùng tên chỉ có thể kích hoạt hiệu ứng này một lần.</t>
+          <t>Kích hoạt Kỹ Năng Echo sẽ tăng Sát Thương Kỹ Năng Echo thêm {0}, tối đa {1} tầng. Các Echo cùng tên chỉ có thể kích hoạt hiệu ứng này một lần.</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Gây Trầy Băng Giá sẽ tăng Sát Thương Băng Giá thêm {0} trong {1} giây, có thể chồng chất lên đến {2} tầng.</t>
+          <t>Gây Glacio Chafe sẽ tăng Sát Thương Băng Giá thêm {0} trong {1} giây, có thể chồng chất lên đến {2} tầng.</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Core Resonance</t>
+          <t>Lõi Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Core Glacio Chafe</t>
+          <t>Lõi Xước Băng Giá</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Core Bùng Nổ Fusion</t>
+          <t>Lõi Bùng Nổ Hợp Nhất</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Tăng Sát Thương Bounce</t>
+          <t>Tăng Sát Thương Nảy</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Thêm Sát Thương Power Strike</t>
+          <t>Thêm Sát Thương Đòn Tấn Công Mạnh</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tăng DMG Kỹ Năng</t>
+          <t>Tăng DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Bonus Sát Thương Rush</t>
+          <t>Thưởng Sát Thương Xông Pha</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Thế Giới Cải Tạo</t>
+          <t>Kỹ Năng Thủ Lĩnh: Thế Giới Đổi Thay</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Passive - Cogitation Model gây gấp đôi sát thương.
+          <t>Thụ Động - Mô Hình Suy Tư gây gấp đôi DMG.
 Chỉ có hiệu lực ở vị trí Đội Trưởng.</t>
         </is>
       </c>
@@ -9502,8 +9502,8 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Tương Lị Yao Dodgem ra &lt;color=#f97507&gt;{0}&lt;/color&gt; Khối Siêu Lập Phương làm vật phẩm thu thập.
-Thu thập một Khối Siêu Lập Phương sẽ tăng Sát Thương toàn đội thêm &lt;color=#f97507&gt;{1}&lt;/color&gt; và Movement Speed thêm &lt;color=#f97507&gt;{2}&lt;/color&gt; trong &lt;color=#f97507&gt;{4}s&lt;/color&gt;, có thể chồng chất lên đến &lt;color=#f97507&gt;{3}&lt;/color&gt; lần.</t>
+          <t>Tương Lị Dao ném ra &lt;color=#f97507&gt;{0}&lt;/color&gt; Khối Siêu Lập Phương làm vật phẩm thu thập.
+Thu thập một Khối Siêu Lập Phương sẽ tăng Sát Thương toàn đội thêm &lt;color=#f97507&gt;{1}&lt;/color&gt; và Tốc Độ Di Chuyển thêm &lt;color=#f97507&gt;{2}&lt;/color&gt; trong &lt;color=#f97507&gt;{4} giây&lt;/color&gt;, có thể chồng chất lên đến &lt;color=#f97507&gt;{3}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Mỗi lần va chạm với kẻ địch sẽ gây thêm Sát Thương khi nảy ra bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công của Xiangli Yao.</t>
+          <t>Mỗi lần va chạm với kẻ địch sẽ gây thêm Sát Thương khi nảy ra bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK của Xiangli Yao.</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Thiên Tài Đột Phá</t>
+          <t>Kỹ Năng Thủ Lĩnh: Đòn Phá Bất Ngờ</t>
         </is>
       </c>
     </row>
@@ -9766,8 +9766,8 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Summon Cuộn Tranh phục hồi HP cho cả đội bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của Zhezhi.
-Trong &lt;color=#f97507&gt;{3}s&lt;/color&gt;, Cuộn Tranh giải phóng &lt;color=#f97507&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; Dấu Ấn Ảo mỗi giây, gây Sát Thương Bật bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; HP tối đa của Zhezhi.</t>
+          <t>Triệu hồi Cuộn Tranh phục hồi HP cho cả đội bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của Zhezhi.
+Trong &lt;color=#f97507&gt;{3} giây&lt;/color&gt;, Cuộn Tranh giải phóng &lt;color=#f97507&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; Dấu Ấn Ảo mỗi giây, gây Sát Thương Bật bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; HP tối đa của Zhezhi.</t>
         </is>
       </c>
     </row>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Increase Crit. DMG của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt;.
+          <t>Tăng Crit. DMG của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt;.
 Mỗi lần va chạm với kẻ địch sẽ hồi HP cho cả đội bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; HP tối đa của Zhezhi.</t>
         </is>
       </c>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Đòn Phá Hủy</t>
+          <t>Kỹ Năng Thủ Lĩnh: Đòn Phá Tan</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Di chuyển đến vị trí mục tiêu và triệu hồi vòng Tre Mực, tăng Movement Speed và gây Sát Thương Bật lại bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; Tấn Công mỗi &lt;color=#f97507&gt;{0}s&lt;/color&gt;. Hiệu ứng kéo dài trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;.</t>
+          <t>Di chuyển đến vị trí mục tiêu và triệu hồi vòng Tre Mực, tăng Tốc Độ Di Chuyển và gây Sát Thương Bật lại bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; ATK mỗi &lt;color=#f97507&gt;{0} giây&lt;/color&gt;. Hiệu ứng kéo dài trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate cho toàn đội &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+          <t>Tăng Crit. Rate cho toàn đội &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Skill Đội trưởng: Qingloong Xuất Chiến</t>
+          <t>Kỹ năng Đội trưởng: Thanh Long Xuất Chiến</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Đội nhận hiệu ứng Lao Vút của Loong: Khi va chạm xuyên qua kẻ địch, gây Sát Thương Đột Kích bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; Tấn Công của Jiyan cho kẻ địch xung quanh mỗi &lt;color=#f97507&gt;{0}s&lt;/color&gt;, kéo dài trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;.</t>
+          <t>Đội nhận hiệu ứng Lao Vút của Loong: Khi va chạm xuyên qua kẻ địch, gây Sát Thương Đột Kích bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; ATK của Jiyan cho kẻ địch xung quanh mỗi &lt;color=#f97507&gt;{0} giây&lt;/color&gt;, kéo dài trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate cho toàn đội &lt;color=#f97507&gt;{0}&lt;/color&gt; khi Loong đang trong trạng thái Dash.</t>
+          <t>Tăng Crit. Rate cho toàn đội &lt;color=#f97507&gt;{0}&lt;/color&gt; khi Loong đang trong trạng thái Dash.</t>
         </is>
       </c>
     </row>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Ánh Sáng Trung Thành</t>
+          <t>Kỹ Năng Thủ Lĩnh: Ánh Sáng Trung Thành</t>
         </is>
       </c>
     </row>
@@ -10422,8 +10422,8 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Lao Vào bằng &lt;color=#f97507&gt;{3}&lt;/color&gt; HP tối đa của Changli. Mỗi giây hồi HP cho đội bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của Changli và trao Flame Feather trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.
-Flame Feather: Đội di chuyển để lại vệt lửa trong &lt;color=#f97507&gt;{4}s&lt;/color&gt;. Kẻ địch chạm vào vệt lửa sẽ chịu Sát Thương Lao Vào bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; HP tối đa của Changli mỗi giây. Sát thương từ nhiều vệt lửa có thể chồng chất.</t>
+          <t>Gây Sát Thương Lao Vào bằng &lt;color=#f97507&gt;{3}&lt;/color&gt; HP tối đa của Changli. Mỗi giây hồi HP cho đội bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của Changli và trao Flame Feather trong &lt;color=#f97507&gt;{1} giây&lt;/color&gt;.
+Flame Feather: Đội di chuyển để lại vệt lửa trong &lt;color=#f97507&gt;{4} giây&lt;/color&gt;. Kẻ địch chạm vào vệt lửa sẽ chịu Sát Thương Lao Vào bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; HP tối đa của Changli mỗi giây. DMG từ nhiều vệt lửa có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Mỗi lần cả đội Rush, tăng Crit. DMG của toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;, có thể tích lũy tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần. Hồi HP cho cả đội bằng &lt;color=#f97507&gt;{3}&lt;/color&gt; HP tối đa của Changli.</t>
+          <t>Mỗi lần cả đội Rush, tăng Crit. DMG của toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt;, có thể tích lũy tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần. Hồi HP cho cả đội bằng &lt;color=#f97507&gt;{3}&lt;/color&gt; HP tối đa của Changli.</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Skill Đội trưởng: Thanh Tẩy Light</t>
+          <t>Kỹ năng Đội trưởng: Thanh Tẩy Ánh Sáng</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Đội nhận hiệu ứng Ánh Sáng Rực: Khi va chạm xuyên qua kẻ địch, phóng &lt;color=#f97507&gt;{0}&lt;/color&gt; tia laser giao nhau gây Sát Thương Đột Kích bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; Tấn Công của Jinhsi mỗi &lt;color=#f97507&gt;{1}s&lt;/color&gt; trong &lt;color=#f97507&gt;{3}s&lt;/color&gt;.</t>
+          <t>Đội nhận hiệu ứng Ánh Sáng Rực: Khi va chạm xuyên qua kẻ địch, phóng &lt;color=#f97507&gt;{0}&lt;/color&gt; tia laser giao nhau gây Sát Thương Đột Kích bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; ATK của Jinhsi mỗi &lt;color=#f97507&gt;{1} giây&lt;/color&gt; trong &lt;color=#f97507&gt;{3} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt; khi cả đội Rush.</t>
+          <t>Tăng Crit. Rate của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1} giây&lt;/color&gt; khi cả đội Rush.</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Bùng Nổ Hỏa Diêm</t>
+          <t>Kỹ năng Đội trưởng: Bộc Phát Hỏa Ngục</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Increase tổng sát thương của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt; khi cả đội Rush, có thể tích lũy tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.
+          <t>Tăng tổng DMG của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt; khi cả đội Rush, có thể tích lũy tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.
 Chỉ có hiệu lực ở vị trí Leader.</t>
         </is>
       </c>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công của Galbrena lên tất cả kẻ địch. Trong &lt;color=#f97507&gt;{3}s&lt;/color&gt; tiếp theo, gây Sát Thương Đột Kích bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; Tấn Công của Galbrena mỗi &lt;color=#f97507&gt;{1}s&lt;/color&gt; lên kẻ địch xung quanh.</t>
+          <t>Gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK của Galbrena lên tất cả kẻ địch. Trong &lt;color=#f97507&gt;{3}s&lt;/color&gt; tiếp theo, gây Sát Thương Đột Kích bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; ATK của Galbrena mỗi &lt;color=#f97507&gt;{1}s&lt;/color&gt; lên kẻ địch xung quanh.</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Increase Sát Thương Rush cho toàn đội &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+          <t>Tăng Sát Thương Rush cho toàn đội &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Ignis Lupa</t>
+          <t>Kỹ năng Đội trưởng: Ignis Lupa</t>
         </is>
       </c>
     </row>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Increase tổng sát thương của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt; khi cả đội gây sát thương Power Strike, có thể tích lũy tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.
+          <t>Tăng tổng DMG của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt; khi cả đội gây DMG Power Strike, có thể tích lũy tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.
 Chỉ có hiệu lực ở vị trí Leader.</t>
         </is>
       </c>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Phóng &lt;color=#f97507&gt;{1}&lt;/color&gt; đòn tấn công, mỗi đòn gây Sát Thương Đòn Trọng Lực bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công. Increase số hit Combo lên &lt;color=#f97507&gt;{2}&lt;/color&gt;.</t>
+          <t>Phóng &lt;color=#f97507&gt;{1}&lt;/color&gt; đòn tấn công, mỗi đòn gây Sát Thương Đòn Trọng Lực bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK. Tăng số hit Combo lên &lt;color=#f97507&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt; khi Lupa đang thi triển Skills.</t>
+          <t>Tăng Crit. Rate của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1} giây&lt;/color&gt; khi Lupa đang thi triển Kỹ Năng.</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Hiện Thân Rạng Rỡ</t>
+          <t>Kỹ năng Đội trưởng: Hiện Thân Thần Quang</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Khi đội sử dụng Flippers để thực hiện Power Strike cấp &lt;color=#f97507&gt;{0}&lt;/color&gt;, &lt;color=#f97507&gt;{1}&lt;/color&gt; hoặc &lt;color=#f97507&gt;{2}&lt;/color&gt;, Iuno bắn &lt;color=#f97507&gt;{3}&lt;/color&gt; Mũi Tên Mặt Trăng, mỗi mũi gây Sát Thương Power Strike tương đương &lt;color=#f97507&gt;{4}&lt;/color&gt;, &lt;color=#f97507&gt;{5}&lt;/color&gt; hoặc &lt;color=#f97507&gt;{6}&lt;/color&gt; HP tối đa của Iuno.
+          <t>Khi đội sử dụng Flippers để thực hiện Power Strike cấp &lt;color=#f97507&gt;{2}&lt;/color&gt;, &lt;color=#f97507&gt;{0}&lt;/color&gt; hoặc &lt;color=#f97507&gt;{1}&lt;/color&gt;, Iuno bắn &lt;color=#f97507&gt;{3}&lt;/color&gt; Mũi Tên Mặt Trăng, mỗi mũi gây Sát Thương Power Strike tương đương &lt;color=#f97507&gt;{4}&lt;/color&gt;, &lt;color=#f97507&gt;{5}&lt;/color&gt; hoặc &lt;color=#f97507&gt;{6}&lt;/color&gt; HP tối đa của Iuno.
 Chỉ có hiệu quả khi ở vị trí Leader.</t>
         </is>
       </c>
@@ -11472,8 +11472,8 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Expand Moon Domain và bắn Moon Arrows, gây sát thương Power Strike bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của Iuno &lt;color=#f97507&gt;{1}&lt;/color&gt; lần. Increase số hit Combo thêm &lt;color=#f97507&gt;{2}&lt;/color&gt;.
-Moon Domain: Increase Crit. DMG của cả đội lên &lt;color=#f97507&gt;{3}&lt;/color&gt; và hồi HP bằng &lt;color=#f97507&gt;{4}&lt;/color&gt; HP tối đa của Iuno mỗi giây trong &lt;color=#f97507&gt;{5}s&lt;/color&gt;.</t>
+          <t>Mở rộng Moon Domain và bắn Moon Arrows, gây DMG Power Strike bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của Iuno &lt;color=#f97507&gt;{1}&lt;/color&gt; lần. Tăng số hit Combo thêm &lt;color=#f97507&gt;{2}&lt;/color&gt;.
+Moon Domain: Tăng Crit. DMG của cả đội lên &lt;color=#f97507&gt;{3}&lt;/color&gt; và hồi HP bằng &lt;color=#f97507&gt;{4}&lt;/color&gt; HP tối đa của Iuno mỗi giây trong &lt;color=#f97507&gt;{5} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Bước Nhảy Tứ Thời</t>
+          <t>Kỹ Năng Thủ Lĩnh: Bước Nhảy Tứ Thời</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Đòn Quyền Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công của Ciaccona lên kẻ địch xung quanh và triệu hồi &lt;color=#f97507&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; Ensemble {Cus:Sap,S=Sylph P=Sylphs SapTag=1} trong &lt;color=#f97507&gt;{4}s&lt;/color&gt;, gây Sát Thương Đòn Quyền Năng bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; Tấn Công của Ciaccona mỗi giây và tăng số lần Combo lên &lt;color=#f97507&gt;{3}&lt;/color&gt;.</t>
+          <t>Gây Sát Thương Đòn Quyền Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK của Ciaccona lên kẻ địch xung quanh và triệu hồi &lt;color=#f97507&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; Ensemble {Cus:Sap,S=Sylph P=Sylphs SapTag=1} trong &lt;color=#f97507&gt;{4} giây&lt;/color&gt;, gây Sát Thương Đòn Quyền Năng bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; ATK của Ciaccona mỗi giây và tăng số lần Combo lên &lt;color=#f97507&gt;{3}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Chinh Phục Hướng Dương</t>
+          <t>Kỹ Năng Thủ Lĩnh: Chinh Phục Hướng Dương</t>
         </is>
       </c>
     </row>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Augusta kích hoạt Kiếm Lời Thề Vĩnh Cửu khi đội sử dụng Vây để thực hiện Đòn Đánh Mạnh Cấp &lt;color=#f97507&gt;{0}&lt;/color&gt;, &lt;color=#f97507&gt;{1}&lt;/color&gt; hoặc &lt;color=#f97507&gt;{2}&lt;/color&gt;, xoay lưỡi kiếm gây Sát Thương Đòn Đánh Mạnh bằng &lt;color=#f97507&gt;{4}&lt;/color&gt;, &lt;color=#f97507&gt;{5}&lt;/color&gt; hoặc &lt;color=#f97507&gt;{6}&lt;/color&gt; Tấn Công của cô mỗi &lt;color=#f97507&gt;{3}s&lt;/color&gt;, đồng thời tăng số hit Combo lên &lt;color=#f97507&gt;{7}&lt;/color&gt;. Hiệu ứng kéo dài &lt;color=#f97507&gt;{8}s&lt;/color&gt; và phạm vi tăng theo cấp Đòn Đánh Mạnh.
+          <t>Augusta kích hoạt Kiếm Lời Thề Vĩnh Cửu khi đội sử dụng Vây để thực hiện Đòn Đánh Mạnh Cấp &lt;color=#f97507&gt;{0}&lt;/color&gt;, &lt;color=#f97507&gt;{1}&lt;/color&gt; hoặc &lt;color=#f97507&gt;{2}&lt;/color&gt;, xoay lưỡi kiếm gây Sát Thương Đòn Đánh Mạnh bằng &lt;color=#f97507&gt;{4}&lt;/color&gt;, &lt;color=#f97507&gt;{5}&lt;/color&gt; hoặc &lt;color=#f97507&gt;{6}&lt;/color&gt; ATK của cô mỗi &lt;color=#f97507&gt;{3}s&lt;/color&gt;, đồng thời tăng số hit Combo lên &lt;color=#f97507&gt;{7}&lt;/color&gt;. Hiệu ứng kéo dài &lt;color=#f97507&gt;{8}s&lt;/color&gt; và phạm vi tăng theo cấp Đòn Đánh Mạnh.
 Chỉ có hiệu lực ở vị trí Leader.</t>
         </is>
       </c>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Mỗi khi đội của bạn va chạm với kẻ địch, gây thêm Sát Thương Đòn Đánh Mạnh bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công và tăng &lt;color=#f97507&gt;{1}&lt;/color&gt; điểm Combo. Hiệu ứng này kéo dài trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;.</t>
+          <t>Mỗi khi đội của bạn va chạm với kẻ địch, gây thêm Sát Thương Đòn Đánh Mạnh bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK và tăng &lt;color=#f97507&gt;{1}&lt;/color&gt; điểm Combo. Hiệu ứng này kéo dài trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12063,8 +12063,8 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate của Sát Thương Đòn Đánh Mạnh cho cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt;.
-Khi đội sử dụng Chân Vịt để thực hiện Đòn Đánh Mạnh, tăng Movement Speed lên &lt;color=#f97507&gt;{1}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;.</t>
+          <t>Tăng Crit. Rate của Sát Thương Đòn Đánh Mạnh cho cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt;.
+Khi đội sử dụng Chân Vịt để thực hiện Đòn Đánh Mạnh, tăng Tốc Độ Di Chuyển lên &lt;color=#f97507&gt;{1}&lt;/color&gt; trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Tầm Nhìn Tháo Gỡ</t>
+          <t>Kỹ Năng Thủ Lĩnh: Ánh Nhìn Giải Đố</t>
         </is>
       </c>
     </row>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Kích hoạt Cưa Máy, gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; Tấn Công của Chisa lên mỗi kẻ địch sau mỗi &lt;color=#f97507&gt;{0}s&lt;/color&gt; và tăng số hit Combo lên &lt;color=#f97507&gt;{2}&lt;/color&gt;. Mỗi mục tiêu chỉ có thể chịu sát thương tối đa &lt;color=#f97507&gt;{3}&lt;/color&gt; lần.</t>
+          <t>Kích hoạt Cưa Máy, gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; ATK của Chisa lên mỗi kẻ địch sau mỗi &lt;color=#f97507&gt;{0} giây&lt;/color&gt; và tăng số hit Combo lên &lt;color=#f97507&gt;{2}&lt;/color&gt;. Mỗi mục tiêu chỉ có thể chịu DMG tối đa &lt;color=#f97507&gt;{3}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt; mỗi khi một thành viên trong đội sử dụng Kỹ Năng.</t>
+          <t>Tăng Crit. Rate của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1} giây&lt;/color&gt; mỗi khi một thành viên trong đội sử dụng Kỹ Năng.</t>
         </is>
       </c>
     </row>
@@ -12391,7 +12391,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Skill Đội trưởng: Critical Protocol</t>
+          <t>Kỹ năng Đội trưởng: Giao Thức Bạo Kích</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Hồi phục thêm &lt;color=#f97507&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Năng Lượng Kỹ Năng P=Năng Lượng Kỹ Năng SapTag=0} mỗi giây, nhưng giảm Speed Energy Regen Đột Kích đi &lt;color=#f97507&gt;{1}&lt;/color&gt; và Movement Speed đi &lt;color=#f97507&gt;{2}&lt;/color&gt;.
+          <t>Hồi phục thêm &lt;color=#f97507&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Năng Lượng Kỹ Năng P=Năng Lượng Kỹ Năng SapTag=0} mỗi giây, nhưng giảm Tốc Độ Hồi Năng Lượng Đột Kích đi &lt;color=#f97507&gt;{1}&lt;/color&gt; và Tốc Độ Di Chuyển đi &lt;color=#f97507&gt;{2}&lt;/color&gt;.
 Chỉ có hiệu lực ở vị trí Đội Trưởng.</t>
         </is>
       </c>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công và chuyển sang Wide Field Observation Mode, tăng Sát Thương Kỹ Năng của toàn đội lên &lt;color=#f97507&gt;{1}s&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;.</t>
+          <t>Gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK và chuyển sang Chế Độ Quan Sát Trường Rộng, tăng Sát Thương Kỹ Năng của toàn đội lên &lt;color=#f97507&gt;{1}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Increase Sát Thương Kỹ Năng cho toàn đội &lt;color=#f97507&gt;{0}&lt;/color&gt; và hồi phục thêm &lt;color=#f97507&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Năng Lượng Kỹ Năng P=Năng Lượng Kỹ Năng SapTag=1} mỗi giây.</t>
+          <t>Tăng Sát Thương Kỹ Năng cho toàn đội &lt;color=#f97507&gt;{0}&lt;/color&gt; và hồi phục thêm &lt;color=#f97507&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=Năng Lượng Kỹ Năng P=Năng Lượng Kỹ Năng SapTag=1} mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Bảng Màu Lynae</t>
+          <t>Kỹ năng Đội trưởng: Bảng Màu Phong Cách Lynae</t>
         </is>
       </c>
     </row>
@@ -12786,8 +12786,8 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Vẽ Phun: Lynae bắn Color Bullets xung quanh, gây sát thương kỹ năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công của cô, và Dodgem &lt;color=#f97507&gt;{1}&lt;/color&gt; Bình Xịt Neon làm vật phẩm nhặt.
-Bình Xịt Neon: Nhặt lên tăng Crit. Rate của toàn đội &lt;color=#f97507&gt;{2}&lt;/color&gt; trong &lt;color=#f97507&gt;{4}s&lt;/color&gt;, có thể chồng chất tối đa &lt;color=#f97507&gt;{3}&lt;/color&gt; lần.</t>
+          <t>Vẽ Phun: Lynae bắn Color Bullets xung quanh, gây DMG kỹ năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK của cô, và ném &lt;color=#f97507&gt;{1}&lt;/color&gt; Bình Xịt Neon làm vật phẩm nhặt.
+Bình Xịt Neon: Nhặt lên tăng Crit. Rate của toàn đội &lt;color=#f97507&gt;{2}&lt;/color&gt; trong &lt;color=#f97507&gt;{4} giây&lt;/color&gt;, có thể chồng chất tối đa &lt;color=#f97507&gt;{3}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Nhảy nào! Increase Movement Speed của đội lên &lt;color=#f97507&gt;{1}&lt;/color&gt; sau mỗi &lt;color=#f97507&gt;{0}s&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{2}&lt;/color&gt;. Va chạm với kẻ địch sẽ đặt lại về &lt;color=#f97507&gt;{3}&lt;/color&gt;.</t>
+          <t>Nhảy nào! Tăng Tốc Độ Di Chuyển của đội lên &lt;color=#f97507&gt;{1}&lt;/color&gt; sau mỗi &lt;color=#f97507&gt;{0} giây&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{2}&lt;/color&gt;. Va chạm với kẻ địch sẽ đặt lại về &lt;color=#f97507&gt;{3}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Tiệc Của Người Dệt Giấc Mơ</t>
+          <t>Kỹ năng Đội trưởng: Tiệc Yến Người Dệt Giấc Mơ</t>
         </is>
       </c>
     </row>
@@ -12983,7 +12983,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Khôi phục toàn bộ Points Kỹ Năng Nổ cho đội ngay khi trận đấu bắt đầu, nhưng giảm tổng Sát Thương của đội đi &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.
+          <t>Khôi phục toàn bộ Điểm Kỹ Năng Nổ cho đội ngay khi trận đấu bắt đầu, nhưng giảm tổng Sát Thương của đội đi &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1} giây&lt;/color&gt;.
 Chỉ có hiệu lực ở vị trí Đội Trưởng.</t>
         </is>
       </c>
@@ -13050,8 +13050,8 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công và Dodgem ra &lt;color=#f97507&gt;{1}&lt;/color&gt; Bù Nhìn Thu Thập.
-Gấu Ôm: Nhặt sẽ hồi &lt;color=#f97507&gt;{2}&lt;/color&gt; Points Kỹ Năng Nổ cho cả đội.</t>
+          <t>Gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK và ném ra &lt;color=#f97507&gt;{1}&lt;/color&gt; Bù Nhìn Thu Thập.
+Gấu Ôm: Nhặt sẽ hồi &lt;color=#f97507&gt;{2}&lt;/color&gt; Điểm Kỹ Năng Nổ cho cả đội.</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Mỗi khi đội thu thập một Pickup, Denia sẽ bắn ra một viên đạn gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công của cô.</t>
+          <t>Mỗi khi đội thu thập một Pickup, Denia sẽ bắn ra một viên đạn gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK của cô.</t>
         </is>
       </c>
     </row>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Thẩm Phán Hoàng Kim</t>
+          <t>Kỹ năng Đội trưởng: Phán Quyết Hoàng Kim</t>
         </is>
       </c>
     </row>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Increase tổng Sát Thương cho toàn đội &lt;color=#f97507&gt;{0}&lt;/color&gt;, nhưng mỗi thành viên trong đội sẽ chịu Sát Thương bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; HP tối đa của Luuk Herssen mỗi giây.
+          <t>Tăng tổng Sát Thương cho toàn đội &lt;color=#f97507&gt;{0}&lt;/color&gt;, nhưng mỗi thành viên trong đội sẽ chịu Sát Thương bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; HP tối đa của Luuk Herssen mỗi giây.
 Chỉ hiệu quả khi ở vị trí Leader.</t>
         </is>
       </c>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP Tối Đa của Luuk Herssen và tạo ra Echo Trạng Thái Rắn. Tổ này giúp đội không bị rơi, tăng Crit. DMG lên &lt;color=#f97507&gt;{1}&lt;/color&gt; và tạo Shield tương đương &lt;color=#f97507&gt;{2}&lt;/color&gt; HP Tối Đa của Luuk Herssen trong &lt;color=#f97507&gt;{3}s&lt;/color&gt;.</t>
+          <t>Gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP Tối Đa của Luuk Herssen và tạo ra Tổ Tacet Trạng Thái Rắn. Tổ này giúp đội không bị rơi, tăng Crit. DMG lên &lt;color=#f97507&gt;{1}&lt;/color&gt; và tạo Khiên tương đương &lt;color=#f97507&gt;{2}&lt;/color&gt; HP Tối Đa của Luuk Herssen trong &lt;color=#f97507&gt;{3}s&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Increase Tái Tạo Shield của Luuk Herssen tương đương &lt;color=#f97507&gt;{0}&lt;/color&gt; hiệu ứng Healing của cậu ấy.</t>
+          <t>Tăng Tái Tạo Khiên của Luuk Herssen tương đương &lt;color=#f97507&gt;{0}&lt;/color&gt; hiệu ứng Hồi Phục của cậu ấy.</t>
         </is>
       </c>
     </row>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Kỹ Năng Thủ Lĩnh: Shared Voyage</t>
+          <t>Kỹ Năng Thủ Lĩnh: Hành Trình Đồng Hành</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Shoot tia laser, gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công.</t>
+          <t>Bắn tia laser, gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK.</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Skills sử dụng lên kẻ địch có HP trên &lt;color=#f97507&gt;{0}&lt;/color&gt; sẽ đảm bảo gây ra Đòn Critical Hit.</t>
+          <t>Kỹ năng sử dụng lên kẻ địch có HP trên &lt;color=#f97507&gt;{0}&lt;/color&gt; sẽ đảm bảo gây ra Đòn Bạo Kích.</t>
         </is>
       </c>
     </row>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Từ Nguyên Solsworn</t>
+          <t>Kỹ Năng Thủ Lĩnh: Ngữ Nguyên Của Solsworn</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Phóng một đòn tấn công diện rộng, gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của Sigrika. Restore &lt;color=#f97507&gt;{1}&lt;/color&gt; điểm Năng Lượng Kỹ Năng cho cả đội và tăng Crit. DMG của toàn đội lên &lt;color=#f97507&gt;{2}&lt;/color&gt; trong &lt;color=#f97507&gt;{3}s&lt;/color&gt;.</t>
+          <t>Phóng một đòn tấn công diện rộng, gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của Sigrika. Hồi phục &lt;color=#f97507&gt;{1}&lt;/color&gt; điểm Năng Lượng Kỹ Năng cho cả đội và tăng Crit. DMG của toàn đội lên &lt;color=#f97507&gt;{2}&lt;/color&gt; trong &lt;color=#f97507&gt;{3} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13967,7 +13967,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Kỹ Năng Đội Trưởng: Springless</t>
+          <t>Kỹ Năng Thủ Lĩnh: Vô Xuân</t>
         </is>
       </c>
     </row>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; Tấn Công của Hiyuki lên tất cả kẻ địch. Trong trạng thái Kỹ Năng Nổ, Hệ Số Sát Thương của đòn tấn công này tăng thêm &lt;color=#f97507&gt;{1}&lt;/color&gt;.</t>
+          <t>Gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; ATK của Hiyuki lên tất cả kẻ địch. Trong trạng thái Kỹ Năng Nổ, Hệ Số Sát Thương của đòn tấn công này tăng thêm &lt;color=#f97507&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong trạng thái Burst. Mỗi lần va chạm với kẻ địch sẽ kích hoạt Blade Arc của Hiyuki, gây sát thương Bounce bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; Tấn Công của cô.
+          <t>Tăng Crit. Rate của cả đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong trạng thái Burst. Mỗi lần va chạm với kẻ địch sẽ kích hoạt Blade Arc của Hiyuki, gây DMG Bounce bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; ATK của cô.
 Nếu không triển khai Healer, tất cả thành viên trong đội sẽ hồi HP bằng &lt;color=#f97507&gt;{2}&lt;/color&gt; HP tối đa của Hiyuki.</t>
         </is>
       </c>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Tiêu hao 4.000 Phiếu Stardock</t>
+          <t>Tiêu tốn 4.000 Phiếu Stardock.</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Tiêu hao 15.000 Phiếu Stardock</t>
+          <t>Tiêu hao tổng cộng 15.000 Phiếu Stardock</t>
         </is>
       </c>
     </row>
@@ -14296,7 +14296,7 @@
       <c r="M212" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Tấn Công toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+ATK toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14363,7 @@
       <c r="M213" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Tấn Công toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+ATK toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14430,7 @@
       <c r="M214" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Tấn Công toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;. Hồi máu +&lt;color=#f97507&gt;{1}&lt;/color&gt;.</t>
+ATK toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;. Hồi máu +&lt;color=#f97507&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14564,7 @@
       <c r="M216" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Tấn Công toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+ATK toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14631,7 +14631,7 @@
       <c r="M217" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Tấn Công toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+ATK toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14698,7 +14698,7 @@
       <c r="M218" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Tấn Công toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;. Hồi máu +&lt;color=#f97507&gt;{1}&lt;/color&gt;.</t>
+ATK toàn đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;. Hồi máu +&lt;color=#f97507&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
       <c r="M220" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Gây Sát thương Bounce làm tăng Tấn Công của cả đội thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.</t>
+Gây DMG Nảy làm tăng ATK của cả đội thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14899,7 @@
       <c r="M221" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Tăng Tấn Công cho toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; khi lao tới trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.</t>
+Tăng ATK cho toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; khi lao tới trong &lt;color=#f97507&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
       <c r="M222" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Sử dụng Skills làm tăng Crit. DMG của toàn đội thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.</t>
+Sử dụng Kỹ Năng làm tăng Crit. DMG của toàn đội thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15033,7 +15033,7 @@
       <c r="M223" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Trong trạng thái Bùng Nổ, Tấn Công của cả đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.</t>
+Trong trạng thái Bùng Nổ, ATK của cả đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15100,7 +15100,7 @@
       <c r="M224" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Sử dụng Skills hồi phục &lt;color=#f97507&gt;{0}&lt;/color&gt; Năng Lượng Skills.</t>
+Sử dụng Kỹ Năng hồi phục &lt;color=#f97507&gt;{0}&lt;/color&gt; Năng Lượng Kỹ Năng.</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       <c r="M225" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Sử dụng Skills hồi phục HP cho tất cả thành viên trong đội bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của người sử dụng.</t>
+Sử dụng Kỹ Năng hồi phục HP cho tất cả thành viên trong đội bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của người sử dụng.</t>
         </is>
       </c>
     </row>
@@ -15234,7 +15234,7 @@
       <c r="M226" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Khi đội sử dụng Đôi Vây để thực hiện Đòn Công Kích, Sát Thương Đòn Công Kích và Sát Thương Lao Tới của toàn đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.</t>
+Khi đội sử dụng Đôi Vây để thực hiện Đòn Công Kích, Sát Thương Đòn Công Kích và Sát Thương Lao Tới của toàn đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15301,7 +15301,7 @@
       <c r="M227" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Tăng Sát Thương Lao Tới cho toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1} lần&lt;/color&gt; chồng chất.</t>
+Tăng Sát Thương Lao Tới cho toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1} lần&lt;/color&gt; chồng chất.</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       <c r="M231" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Mỗi lần sử dụng Skill, Sát thương Skill của cả đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.</t>
+Mỗi lần sử dụng Kỹ năng, DMG Kỹ năng của cả đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -15636,7 +15636,7 @@
       <c r="M232" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Mỗi lần thu thập Vật phẩm Nhặt, Crit. DMG của cả đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.</t>
+Mỗi lần thu thập Vật phẩm Nhặt, DMG Bạo Kích của cả đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -15703,7 +15703,7 @@
       <c r="M233" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Tăng Tấn Công cho toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; khi lao tới.</t>
+Tăng ATK cho toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; khi lao tới.</t>
         </is>
       </c>
     </row>
@@ -15770,7 +15770,7 @@
       <c r="M234" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Sử dụng Skills làm tăng Crit. DMG của toàn đội thêm &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+Sử dụng Kỹ Năng làm tăng Crit. DMG của toàn đội thêm &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15837,7 +15837,7 @@
       <c r="M235" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Trong trạng thái Bùng Nổ, Tấn Công của cả đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+Trong trạng thái Bùng Nổ, ATK của cả đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       <c r="M236" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Sử dụng Skills hồi phục HP cho toàn đội bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của mỗi người.</t>
+Sử dụng Kỹ Năng hồi phục HP cho toàn đội bằng &lt;color=#f97507&gt;{0}&lt;/color&gt; HP tối đa của mỗi người.</t>
         </is>
       </c>
     </row>
@@ -15971,7 +15971,7 @@
       <c r="M237" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Gây sát thương bằng Đòn Tấn Công sẽ tăng thêm Sát thương Đòn Tấn Công thêm &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+Gây DMG bằng Đòn Tấn Công sẽ tăng thêm DMG Đòn Tấn Công thêm &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16373,7 @@
       <c r="M243" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Mỗi lần thu thập Vật phẩm Nhặt, Crit. DMG của cả đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.</t>
+Mỗi lần thu thập Vật phẩm Nhặt, DMG Bạo Kích của cả đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -16439,8 +16439,8 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
-Tấn Công +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
+ATK +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
 HP +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -16574,7 +16574,7 @@
       <c r="M246" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng bổ sung&lt;/size&gt;&lt;/color&gt;
-Sát thương Đòn Tấn Công của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+DMG Đòn Tấn Công của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16640,8 +16640,8 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
-Sát Thương Bật Lại Co-op +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
+Sát Thương Bật Lại Đồng Đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16708,7 +16708,7 @@
       <c r="M248" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng bổ sung&lt;/size&gt;&lt;/color&gt;
-Sát thương Đòn Lao của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+DMG Đòn Lao của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16775,7 +16775,7 @@
       <c r="M249" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng bổ sung&lt;/size&gt;&lt;/color&gt;
-Sát thương Skill của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+DMG Kỹ năng của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
 Crit. Rate +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -16908,8 +16908,8 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
-Tấn Công +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
+ATK +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
 HP +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -17043,7 +17043,7 @@
       <c r="M253" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng bổ sung&lt;/size&gt;&lt;/color&gt;
-Sát thương Đòn Tấn Công của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+DMG Đòn Tấn Công của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17109,8 +17109,8 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
-Sát Thương Bật Lại Co-op +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
+Sát Thương Bật Lại Đồng Đội +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17177,7 +17177,7 @@
       <c r="M255" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng bổ sung&lt;/size&gt;&lt;/color&gt;
-Sát thương Đòn Lao của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+DMG Đòn Lao của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17244,7 +17244,7 @@
       <c r="M256" t="inlineStr">
         <is>
           <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu ứng bổ sung&lt;/size&gt;&lt;/color&gt;
-Sát thương Skill của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+DMG Kỹ năng của đội tăng &lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
 Crit. Rate +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -17377,8 +17377,8 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
-Tấn Công +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
+ATK +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
 HP +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -17511,8 +17511,8 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
-Tấn Công +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
+ATK +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
 HP +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -17645,8 +17645,8 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
-Tấn Công +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
+ATK +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17712,7 +17712,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Effect Bổ Sung&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#5b1d2f&gt;&lt;size=36&gt;Hiệu Ứng Bổ Sung&lt;/size&gt;&lt;/color&gt;
 HP +&lt;color=#f97507&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -17846,8 +17846,8 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
-Khi Cuộn Tranh của Zhezhi đang hoạt động, Crit. DMG của toàn đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; và Cuộn Tranh giải phóng thêm &lt;color=#f97507&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; Ảnh Phantasm {Cus:Sap,S=khác P=khác SapTag=1}.</t>
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
+Khi Cuộn Tranh của Zhezhi đang hoạt động, Sát Thương Bạo Kích của toàn đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; và Cuộn Tranh giải phóng thêm &lt;color=#f97507&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; Ảnh Phantasm {Cus:Sap,S=khác P=khác SapTag=1}.</t>
         </is>
       </c>
     </row>
@@ -17914,9 +17914,9 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
-Khi Qiuyuan sử dụng Skills, Sát Thương Bounce của toàn đội tăng thêm &lt;color=#f97507&gt;{3}&lt;/color&gt; trong &lt;color=#f97507&gt;{4}s&lt;/color&gt;.
-Mỗi lần va chạm với kẻ địch sẽ tăng Crit. Rate của toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.</t>
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
+Khi Qiuyuan sử dụng Kỹ Năng, Sát Thương Bounce của toàn đội tăng thêm &lt;color=#f97507&gt;{3}&lt;/color&gt; trong &lt;color=#f97507&gt;{4} giây&lt;/color&gt;.
+Mỗi lần va chạm với kẻ địch sẽ tăng Crit. Rate của toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
 Khi Dash của Loong đang hoạt động, đội bỏ qua &lt;color=#f97507&gt;{0}&lt;/color&gt; Phòng Ngự của kẻ địch khi gây Sát Thương và nhận thêm &lt;color=#f97507&gt;{1}&lt;/color&gt; Crit. Rate.</t>
         </is>
       </c>
@@ -18050,7 +18050,7 @@
       <c r="M268" t="inlineStr">
         <is>
           <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Tăng Crit. DMG toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt;. Mỗi lần toàn đội Tăng Tốc, sẽ nhận được Feather Lửa trong &lt;color=#f97507&gt;{1}s&lt;/color&gt;.</t>
+Tăng Crit. DMG toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt;. Mỗi lần toàn đội Tăng Tốc, sẽ nhận được Lông Vũ Lửa trong &lt;color=#f97507&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18119,7 +18119,7 @@
         <is>
           <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
 Mỗi lần toàn đội Tăng Tốc, Crit. Rate sẽ tăng vĩnh viễn lên &lt;color=#f97507&gt;{0}&lt;/color&gt;, có thể chồng chất tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.
-Khi đạt &lt;color=#f97507&gt;{2}&lt;/color&gt; tầng, Tăng Tốc còn tăng tổng Sát Thương toàn đội lên &lt;color=#f97507&gt;{3}&lt;/color&gt; trong &lt;color=#f97507&gt;{4}s&lt;/color&gt;.</t>
+Khi đạt &lt;color=#f97507&gt;{2}&lt;/color&gt; tầng, Tăng Tốc còn tăng tổng Sát Thương toàn đội lên &lt;color=#f97507&gt;{3}&lt;/color&gt; trong &lt;color=#f97507&gt;{4} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18185,8 +18185,8 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
-Tăng Sát Thương Rush của toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt;. Mỗi lần đội thực hiện Rush, Năng Lượng Rush được hồi phục &lt;color=#f97507&gt;{1}&lt;/color&gt; điểm, kích hoạt &lt;color=#f97507&gt;&lt;SapTag=3&gt;{3}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi &lt;color=#f97507&gt;{2}s&lt;/color&gt;.</t>
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
+Tăng Sát Thương Rush của toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt;. Mỗi lần đội thực hiện Rush, Năng Lượng Rush được hồi phục &lt;color=#f97507&gt;{1}&lt;/color&gt; điểm, kích hoạt &lt;color=#f97507&gt;&lt;SapTag=3&gt;{3}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi &lt;color=#f97507&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18252,8 +18252,8 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
-Khi Lupa sử dụng Skills, Crit. Rate của toàn đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; và Tổng Sát Thương tăng thêm &lt;color=#f97507&gt;{1}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;.</t>
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
+Khi Lupa sử dụng Kỹ Năng, Crit. Rate của toàn đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; và Tổng Sát Thương tăng thêm &lt;color=#f97507&gt;{1}&lt;/color&gt; trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18455,7 +18455,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
 Tăng Crit. Rate của toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; và giảm số lần đánh Combo cần thiết để thực hiện Power Strike xuống &lt;color=#f97507&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -18525,7 +18525,7 @@
         <is>
           <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
 Xác định điểm yếu của kẻ địch và tăng vĩnh viễn Crit. Rate toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt; mỗi giây, có thể chồng chất tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.
-Khi Chisa tấn công kẻ địch bằng Chainsaw, DEF của tất cả kẻ địch sẽ giảm &lt;color=#f97507&gt;{2}&lt;/color&gt; trong &lt;color=#f97507&gt;{3}s&lt;/color&gt;.</t>
+Khi Chisa tấn công kẻ địch bằng Cưa Xích, DEF của tất cả kẻ địch sẽ giảm &lt;color=#f97507&gt;{2}&lt;/color&gt; trong &lt;color=#f97507&gt;{3} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18592,9 +18592,9 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
-Khi ở Wide Field Observation Mode, toàn đội gây thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; Sát Thương Kỹ Năng.
-Mornye bắn tia laser mỗi khi va chạm với kẻ địch, gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; Tấn Công.</t>
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
+Khi ở Chế Độ Quan Sát Trường Rộng, toàn đội gây thêm &lt;color=#f97507&gt;{0}&lt;/color&gt; Sát Thương Kỹ Năng.
+Mornye bắn tia laser mỗi khi va chạm với kẻ địch, gây Sát Thương Kỹ Năng bằng &lt;color=#f97507&gt;{1}&lt;/color&gt; ATK.</t>
         </is>
       </c>
     </row>
@@ -18663,7 +18663,7 @@
         <is>
           <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
 Mỗi tầng của Bình Xịt Neon Lynae sẽ tăng thêm Crit. Rate toàn đội lên &lt;color=#f97507&gt;{0}&lt;/color&gt;.
-Thu thập bất kỳ vật phẩm nào sẽ tăng tổng Sát Thương toàn đội lên &lt;color=#f97507&gt;{1}&lt;/color&gt; trong &lt;color=#f97507&gt;{2}s&lt;/color&gt;.</t>
+Thu thập bất kỳ vật phẩm nào sẽ tăng tổng Sát Thương toàn đội lên &lt;color=#f97507&gt;{1}&lt;/color&gt; trong &lt;color=#f97507&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
       <c r="M278" t="inlineStr">
         <is>
           <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu ứng ROM&lt;/size&gt;&lt;/color&gt;
-Thu thập Bù Nhìn sẽ khôi phục thêm &lt;color=#f97507&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; Năng Lượng Bùng Nổ {Cus:Sap,S=Points P=Points SapTag=0} và tăng Sát Thương toàn đội lên &lt;color=#f97507&gt;{1}&lt;/color&gt; trong &lt;color=#f97507&gt;{3}s&lt;/color&gt;, có thể chồng chất tối đa &lt;color=#f97507&gt;{2}&lt;/color&gt; lần.</t>
+Thu thập Bù Nhìn sẽ khôi phục thêm &lt;color=#f97507&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; Năng Lượng Bùng Nổ {Cus:Sap,S=Điểm P=Điểm SapTag=0} và tăng Sát Thương toàn đội lên &lt;color=#f97507&gt;{1}&lt;/color&gt; trong &lt;color=#f97507&gt;{3} giây&lt;/color&gt;, có thể chồng chất tối đa &lt;color=#f97507&gt;{2}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
 Khi Trường Ichor Trạng Thái Rắn hoạt động, Crit. DMG của toàn đội tăng thêm &lt;color=#f97507&gt;{0}&lt;/color&gt;.
 Khi HP của đội dưới &lt;color=#f97507&gt;{1}&lt;/color&gt;, họ chịu ít hơn &lt;color=#f97507&gt;{2}&lt;/color&gt; Sát Thương. Trong trạng thái Burst, hiệu ứng Giảm Sát Thương được nhân đôi.</t>
         </is>
@@ -18866,9 +18866,9 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
-Khi Pinball sử dụng Skills, Sát Thương Skills của Aemeath tăng vĩnh viễn &lt;color=#f97507&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.
-Crit. Rate của Skills Pinball khi tấn công kẻ địch có HP dưới &lt;color=#f97507&gt;{2}&lt;/color&gt; tăng thêm &lt;color=#f97507&gt;{3}&lt;/color&gt;.</t>
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
+Khi Pinball sử dụng Kỹ Năng, Sát Thương Kỹ Năng của Aemeath tăng vĩnh viễn &lt;color=#f97507&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt;, tối đa &lt;color=#f97507&gt;{1}&lt;/color&gt; lần.
+Crit. Rate của Kỹ Năng Pinball khi tấn công kẻ địch có HP dưới &lt;color=#f97507&gt;{2}&lt;/color&gt; tăng thêm &lt;color=#f97507&gt;{3}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
 Kỹ Năng của Sigrika bổ sung hồi phục &lt;color=#f97507&gt;{0}&lt;/color&gt; điểm Năng Lượng Kỹ Năng cho đội và tăng thêm Crit. DMG của toàn đội lên &lt;color=#f97507&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -19002,9 +19002,9 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Effect ROM&lt;/size&gt;&lt;/color&gt;
-Hồi phục &lt;color=#f97507&gt;{0}&lt;/color&gt; Points Burst khi bắt đầu trận đấu và tăng Tỷ Lệ Critical Hit của toàn đội lên &lt;color=#f97507&gt;{1}&lt;/color&gt;.
-Trong trạng thái Burst, mọi đòn tấn công của đội đều đảm bảo gây Critical Hit. Mỗi lần đội va chạm với kẻ địch, Blade Arcs sẽ bắn ra theo &lt;color=#f97507&gt;{2}&lt;/color&gt; hướng khác nhau.</t>
+          <t>&lt;color=#723a2e&gt;&lt;size=36&gt;Hiệu Ứng ROM&lt;/size&gt;&lt;/color&gt;
+Hồi phục &lt;color=#f97507&gt;{0}&lt;/color&gt; Điểm Burst khi bắt đầu trận đấu và tăng Tỷ Lệ Bạo Kích của toàn đội lên &lt;color=#f97507&gt;{1}&lt;/color&gt;.
+Trong trạng thái Burst, mọi đòn tấn công của đội đều đảm bảo gây Bạo Kích. Mỗi lần đội va chạm với kẻ địch, Blade Arcs sẽ bắn ra theo &lt;color=#f97507&gt;{2}&lt;/color&gt; hướng khác nhau.</t>
         </is>
       </c>
     </row>
@@ -19069,7 +19069,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Quyền Trượng Cộng Hưởng Aurora I</t>
+          <t>Pháp Trượng Cộng Hưởng Aurora I</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Quyền Trượng Cộng Hưởng Aurora II</t>
+          <t>Pháp Trượng Cộng Hưởng Aurora II</t>
         </is>
       </c>
     </row>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Quyền Trượng Cộng Hưởng Aurora III</t>
+          <t>Pháp Trượng Cộng Hưởng Aurora III</t>
         </is>
       </c>
     </row>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Tăng DMG Bật.</t>
+          <t>Tăng Sát Thương Bật Lại.</t>
         </is>
       </c>
     </row>
@@ -19589,7 +19589,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Tăng tốc độ di chuyển và sát thương cho cả đội.</t>
+          <t>Tăng tốc độ di chuyển và DMG cho cả đội.</t>
         </is>
       </c>
     </row>
@@ -19654,7 +19654,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Tăng DMG Bật.</t>
+          <t>Tăng Sát Thương Bật Lại.</t>
         </is>
       </c>
     </row>
@@ -19719,7 +19719,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Tăng tổng sát thương gây ra và giảm sát thương nhận vào.</t>
+          <t>Tăng tổng DMG gây ra và giảm DMG nhận vào.</t>
         </is>
       </c>
     </row>
@@ -20369,7 +20369,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Tăng DMG Tấn Công Đột Kích.</t>
+          <t>Tăng Sát Thương Lao Đâm.</t>
         </is>
       </c>
     </row>
@@ -20434,7 +20434,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Phục hồi HP mỗi giây.</t>
+          <t>Hồi phục HP mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -20759,7 +20759,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Tăng Crit. Rate và tổng sát thương.</t>
+          <t>Tăng Crit. Rate và tổng DMG.</t>
         </is>
       </c>
     </row>
@@ -20954,7 +20954,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Tăng DMG Power Strike.</t>
+          <t>Tăng Sát Thương Đòn Đánh Mạnh.</t>
         </is>
       </c>
     </row>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Tăng DMG Power Strike.</t>
+          <t>Tăng Sát Thương Đòn Đánh Mạnh.</t>
         </is>
       </c>
     </row>
@@ -21474,7 +21474,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Đảm bảo Critical Hit vào mục tiêu có HP trên 60%.</t>
+          <t>Đảm bảo Bạo Kích vào mục tiêu có HP trên 60%.</t>
         </is>
       </c>
     </row>
@@ -21604,7 +21604,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Tăng tốc độ hồi phục Năng Lượng Kỹ Năng. Giảm Sát Thương Đột Kích và Movement Speed.</t>
+          <t>Tăng tốc độ hồi phục Năng Lượng Kỹ Năng. Giảm Sát Thương Đột Kích và Tốc Độ Di Chuyển.</t>
         </is>
       </c>
     </row>
@@ -22189,7 +22189,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Phục hồi HP mỗi giây.</t>
+          <t>Hồi phục HP mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -22254,7 +22254,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Giảm tổng DMG</t>
+          <t>Giảm tổng Sát Thương</t>
         </is>
       </c>
     </row>
@@ -22384,7 +22384,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Tăng tổng sát thương, nhưng mỗi giây sẽ nhận sát thương.</t>
+          <t>Tăng tổng DMG, nhưng mỗi giây sẽ nhận DMG.</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>{PlayerName}, Miko của Forte Hoa Anh Đào Lửa đã tạo ra một số môi trường kỳ lạ trong Sealed Fissure. Có lẽ cậu sẽ cần làm tan băng trước khi khôi phục những loài thực vật cổ đại.</t>
+          <t>{PlayerName}, Miko của Forte Hoa Anh Đào Lửa đã tạo ra một số môi trường kỳ lạ trong Khe Nứt Bị Phong Ấn. Có lẽ cậu sẽ cần làm tan băng trước khi khôi phục những loài thực vật cổ đại.</t>
         </is>
       </c>
     </row>
@@ -22515,8 +22515,8 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Hoàn thành &lt;color=#ffe65a&gt;challenges with the "Dimmr Plains Survey" tag&lt;/color&gt; tại &lt;color=#ffe65a&gt;Silent Crag&lt;/color&gt; để nhận vật liệu phục hồi Voidbane Eldertree.
-Khi cây được phục hồi hoàn toàn, bạn sẽ nhận được Quả Prism &lt;texture=/Game/Aki/UI/UIResources/Common/Image/IconC80/T_IconC80_jijian_01_UI.T_IconC80_jijian_01_UI,0.5/&gt;x1.</t>
+          <t>Hoàn thành &lt;color=#ffe65a&gt;thử thách có thẻ "Khảo Sát Đồng Bằng Dimmr"&lt;/color&gt; tại &lt;color=#ffe65a&gt;Vách Đá Vắng Lặng&lt;/color&gt; để nhận vật liệu phục hồi Voidbane Eldertree.
+Khi cây được phục hồi hoàn toàn, bạn sẽ nhận được Quả Lăng Kính &lt;texture=/Game/Aki/UI/UIResources/Common/Image/IconC80/T_IconC80_jijian_01_UI.T_IconC80_jijian_01_UI,0.5/&gt;x1.</t>
         </is>
       </c>
     </row>
@@ -22582,8 +22582,8 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Hoàn thành &lt;color=#ffe65a&gt;challenges with the "Dimmr Plains Survey" tag&lt;/color&gt; tại &lt;color=#ffe65a&gt;Sealed Fissure&lt;/color&gt; để nhận vật liệu phục hồi Voidbane Eldertree.
-Khi cây được phục hồi hoàn toàn, bạn sẽ nhận được Quả Prism &lt;texture=/Game/Aki/UI/UIResources/Common/Image/IconC80/T_IconC80_jijian_01_UI.T_IconC80_jijian_01_UI,0.5/&gt;x1.</t>
+          <t>Hoàn thành &lt;color=#ffe65a&gt;thử thách có thẻ "Khảo Sát Đồng Bằng Dimmr"&lt;/color&gt; tại &lt;color=#ffe65a&gt;Khe Nứt Bị Phong Ấn&lt;/color&gt; để nhận vật liệu phục hồi Voidbane Eldertree.
+Khi cây được phục hồi hoàn toàn, bạn sẽ nhận được Quả Lăng Kính &lt;texture=/Game/Aki/UI/UIResources/Common/Image/IconC80/T_IconC80_jijian_01_UI.T_IconC80_jijian_01_UI,0.5/&gt;x1.</t>
         </is>
       </c>
     </row>
@@ -22649,8 +22649,8 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Hoàn thành &lt;color=#ffe65a&gt;Exploration Quest&lt;/color&gt; hoặc &lt;color=#ffe65a&gt;challenges with the "Dimmr Plains Survey" tag&lt;/color&gt; tại &lt;color=#ffe65a&gt;Dimmr Deep&lt;/color&gt; để nhận vật liệu phục hồi Voidbane Eldertree.
-Khi cây được phục hồi hoàn toàn, bạn sẽ nhận được Quả Prism &lt;texture=/Game/Aki/UI/UIResources/Common/Image/IconC80/T_IconC80_jijian_01_UI.T_IconC80_jijian_01_UI,0.5/&gt;x1.</t>
+          <t>Hoàn thành &lt;color=#ffe65a&gt;Nhiệm Vụ Thám Hiểm&lt;/color&gt; hoặc &lt;color=#ffe65a&gt;thử thách có thẻ "Khảo Sát Đồng Bằng Dimmr"&lt;/color&gt; tại &lt;color=#ffe65a&gt;Vực Sâu Dimmr&lt;/color&gt; để nhận vật liệu phục hồi Voidbane Eldertree.
+Khi cây được phục hồi hoàn toàn, bạn sẽ nhận được Quả Lăng Kính &lt;texture=/Game/Aki/UI/UIResources/Common/Image/IconC80/T_IconC80_jijian_01_UI.T_IconC80_jijian_01_UI,0.5/&gt;x1.</t>
         </is>
       </c>
     </row>
@@ -22716,8 +22716,8 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Hoàn thành &lt;color=#ffe65a&gt;Exploration Quest&lt;/color&gt; hoặc &lt;color=#ffe65a&gt;challenges with the "Dimmr Plains Survey" tag&lt;/color&gt; tại &lt;color=#ffe65a&gt;Solisia Landing&lt;/color&gt; để nhận vật liệu phục hồi Voidbane Eldertree.
-Khi cây được phục hồi hoàn toàn, bạn sẽ nhận được Quả Prism &lt;texture=/Game/Aki/UI/UIResources/Common/Image/IconC80/T_IconC80_jijian_01_UI.T_IconC80_jijian_01_UI,0.5/&gt;x1.</t>
+          <t>Hoàn thành &lt;color=#ffe65a&gt;Nhiệm Vụ Thám Hiểm&lt;/color&gt; hoặc &lt;color=#ffe65a&gt;thử thách có thẻ "Khảo Sát Đồng Bằng Dimmr"&lt;/color&gt; tại &lt;color=#ffe65a&gt;Bãi Đáp Solisia&lt;/color&gt; để nhận vật liệu phục hồi Voidbane Eldertree.
+Khi cây được phục hồi hoàn toàn, bạn sẽ nhận được Quả Lăng Kính &lt;texture=/Game/Aki/UI/UIResources/Common/Image/IconC80/T_IconC80_jijian_01_UI.T_IconC80_jijian_01_UI,0.5/&gt;x1.</t>
         </is>
       </c>
     </row>
@@ -22793,16 +22793,16 @@
       <c r="M340" t="inlineStr">
         <is>
           <t>Về Nhiệm Vụ
-Startorch Academy và Bộ tộc Roya đã hợp tác thiết lập căn cứ tại Dimmr Plains, khởi động một chuyến thám hiểm khoa học chung vào vùng đất cô lập từ lâu này. Mục tiêu bao gồm thu thập dữ liệu môi trường, phục hồi mẫu thực vật cổ đại và các bộ phận Exostrider, cũng như khắc phục thiệt hại sinh thái do Void Storm gây ra. Thành quả của chiến dịch này sẽ thúc đẩy đáng kể nghiên cứu sinh thái và phục hồi môi trường sống tại Lahai-Roi.
+Học viện Startorch và Bộ tộc Roya đã hợp tác thiết lập căn cứ tại Đồng Bằng Dimmr, khởi động một chuyến thám hiểm khoa học chung vào vùng đất cô lập từ lâu này. Mục tiêu bao gồm thu thập dữ liệu môi trường, phục hồi mẫu thực vật cổ đại và các bộ phận Exostrider, cũng như khắc phục thiệt hại sinh thái do Bão Hư Không gây ra. Thành quả của chiến dịch này sẽ thúc đẩy đáng kể nghiên cứu sinh thái và phục hồi môi trường sống tại Lahai-Roi.
 Bạn nhận được tin nhắn từ I.R.I.S., mời tham gia chuyến thám hiểm đầu tiên...
 Điều Kiện Tham Gia
 Hoàn thành Nhiệm Vụ Chính "Ánh Sao Từ Quá Khứ" để mở khóa.
 Nội Quy
-Một loài cây cổ đại hoàn toàn mới đã được phát hiện tại bốn khu vực của Dimmr Plains. Khoa Năng Lượng Light chính thức đặt tên chúng là Cổ Thụ Kháng Hư Không. Do tác động kép từ Solvein Heartwood và ô nhiễm Void Storm, những cá thể này phát triển còi cọc và dị dạng. Đội thám hiểm đã lên kế hoạch khôi phục chúng về trạng thái khỏe mạnh.
+Một loài cây cổ đại hoàn toàn mới đã được phát hiện tại bốn khu vực của Đồng Bằng Dimmr. Khoa Năng Lượng Ánh Sáng chính thức đặt tên chúng là Cổ Thụ Kháng Hư Không. Do tác động kép từ Solvein Heartwood và ô nhiễm Bão Hư Không, những cá thể này phát triển còi cọc và dị dạng. Đội thám hiểm đã lên kế hoạch khôi phục chúng về trạng thái khỏe mạnh.
 Hợp tác với các thành viên Đội Khảo Sát để dọn sạch ô nhiễm Vật Chất Hư Không và các bất thường khác trong khu vực, hoàn tất công tác chuẩn bị.
-Vật liệu cần thiết, "Thuốc Restoration", có thể thu thập qua các nhiệm vụ thám hiểm và thử thách trong từng khu vực. Giao đủ số lượng Thuốc Restoration cho một khu vực để khôi phục Cổ Thụ Kháng Hư Không tại đó.
+Vật liệu cần thiết, "Thuốc Phục Hồi", có thể thu thập qua các nhiệm vụ thám hiểm và thử thách trong từng khu vực. Giao đủ số lượng Thuốc Phục Hồi cho một khu vực để khôi phục Cổ Thụ Kháng Hư Không tại đó.
 Hoàn thành việc khôi phục một cây sẽ nhận được Trái Cầu Tinh Thể hiếm, có thể giao cho I.R.I.S. tại Trại Cơ Bản để thúc đẩy tiến độ thám hiểm và mở rộng căn cứ.
-Sau khi hoàn tất tất cả hoạt động khôi phục trên Dimmr Plains và nâng cấp Trại Cơ Bản lên Cấp 5, luồng năng lượng từ Solvein Heartwood sẽ được tăng cường, khiến Dimmr Plains lại rực sáng như xưa.</t>
+Sau khi hoàn tất tất cả hoạt động khôi phục trên Đồng Bằng Dimmr và nâng cấp Trại Cơ Bản lên Cấp 5, luồng năng lượng từ Solvein Heartwood sẽ được tăng cường, khiến Đồng Bằng Dimmr lại rực sáng như xưa.</t>
         </is>
       </c>
     </row>
@@ -22932,7 +22932,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch Round 3 của Singularity Expansion trong Endstate Matrix</t>
+          <t>Đánh bại kẻ địch Vòng 3 của Mở Rộng Điểm Kỳ Dị trong Ma Trận Tận Thế</t>
         </is>
       </c>
     </row>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Mỗi 20 đòn tấn công liên tiếp sẽ triệu hồi thêm một Ngọn Lửa Thiên Thạch, gây sát thương bằng {0} Tấn Công, kích hoạt mỗi {1} giây một lần.</t>
+          <t>Mỗi 20 đòn tấn công liên tiếp sẽ triệu hồi thêm một Ngọn Lửa Thiên Thạch, gây DMG bằng {0} ATK, kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -23192,7 +23192,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Mỗi 10 đòn Critical Hit sẽ triệu hồi thêm một Ngọn Lửa Thiên Thạch, gây sát thương bằng {0} Tấn Công, kích hoạt mỗi {1} giây một lần.</t>
+          <t>Mỗi 10 đòn Bạo Kích sẽ triệu hồi thêm một Ngọn Lửa Thiên Thạch, gây DMG bằng {0} ATK, kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -23322,7 +23322,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Cứ mỗi {0} giây trong chiến đấu mà không nhận sát thương, Crit. DMG sẽ tăng {1}, tối đa {2} lần. Nhận sát thương sẽ mất &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=3}.</t>
+          <t>Cứ mỗi {0} giây trong chiến đấu mà không nhận DMG, Crit. DMG sẽ tăng {1}, tối đa {2} lần. Nhận DMG sẽ mất &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=3}.</t>
         </is>
       </c>
     </row>
@@ -23387,7 +23387,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Tấn công liên tiếp sẽ tăng Tấn Công thêm {0} và Phòng Ngự thêm {1} cho Resonator đang hoạt động, tối đa {2} lần.</t>
+          <t>ATK liên tiếp sẽ tăng ATK thêm {0} và Phòng Ngự thêm {1} cho Resonator đang hoạt động, tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -23517,7 +23517,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Cứ mỗi {0} giây ra đòn liên tiếp sẽ hồi HP bằng {1} Tấn Công.</t>
+          <t>Cứ mỗi {0} giây ra đòn liên tiếp sẽ hồi HP bằng {1} ATK.</t>
         </is>
       </c>
     </row>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Tăng {0} Sát Thương Basic Attack.</t>
+          <t>Tăng {0} Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Mỗi 20 đòn tấn công liên tiếp sẽ tăng {0} sát thương cho Resonance Skill hoặc Resonance Liberation tiếp theo.</t>
+          <t>Mỗi 20 đòn tấn công liên tiếp sẽ tăng {0} DMG cho Resonance Skill hoặc Resonance Liberation tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -23907,7 +23907,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Bạo kích tăng Sát Thương Heavy Attack thêm {0} trong {2} giây, tối đa {1} lần cộng dồn.</t>
+          <t>Bạo kích tăng Sát Thương Đòn Heavy Attack thêm {0} trong {2} giây, tối đa {1} lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Mỗi Fusion thu thập được tăng Tấn Công thêm {0}, tối đa {1}.</t>
+          <t>Mỗi Fusion thu thập được tăng ATK thêm {0}, tối đa {1}.</t>
         </is>
       </c>
     </row>
@@ -24167,7 +24167,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Bạo kích tăng Tấn Công thêm {0} trong {1} giây, tối đa {2} lần cộng dồn.</t>
+          <t>Bạo kích tăng ATK thêm {0} trong {1} giây, tối đa {2} lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -24297,7 +24297,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Dodge thành công tăng Crit. Rate của Resonator đang hoạt động lên {0} trong {1} giây.</t>
+          <t>Né tránh thành công tăng Crit. Rate của Resonator đang hoạt động lên {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -24362,7 +24362,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Attack mạnh trúng mục tiêu tăng Crit. DMG thêm {0} trong {1} giây, tối đa {2} lần.</t>
+          <t>Tấn công mạnh trúng mục tiêu tăng Crit. DMG thêm {0} trong {1} giây, tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -24427,7 +24427,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>ATK tăng thêm {0}.</t>
+          <t>ATK tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -24492,7 +24492,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Tăng {0} Sát Thương Basic Attack.</t>
+          <t>Tăng {0} Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Sát thương Heavy Attack tăng thêm {0}.</t>
+          <t>DMG Heavy Attack tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -24622,7 +24622,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Resonance Skill trúng đích tăng Sát Thương thêm {0} trong {1} giây.</t>
+          <t>Kỹ năng Cộng Hưởng trúng đích tăng Sát Thương thêm {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -24687,7 +24687,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Khi Resonator đang hoạt động được bảo vệ bởi khiên, Basic Attack hoặc Nặng sẽ triệu hồi Chuông Băng khi trúng đích, gây Sát Thương bằng {0} HP tối đa. Cooldown: {1} giây.</t>
+          <t>Khi Resonator đang hoạt động được bảo vệ bởi khiên, Đòn Tấn Công Cơ Bản hoặc Nặng sẽ triệu hồi Chuông Băng khi trúng đích, gây Sát Thương bằng {0} HP tối đa. Thời gian hồi: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -24752,7 +24752,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Khi Resonator đang hoạt động được bảo vệ bởi khiên, mỗi lần chịu Sát Thương sẽ triệu hồi Chuông Băng xung quanh, gây Sát Thương bằng {0} HP tối đa. Cooldown: {1} giây.</t>
+          <t>Khi Resonator đang hoạt động được bảo vệ bởi khiên, mỗi lần chịu Sát Thương sẽ triệu hồi Chuông Băng xung quanh, gây Sát Thương bằng {0} HP tối đa. Thời gian hồi: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -24817,7 +24817,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Khi Resonator đang hoạt động được bảo vệ bởi khiên, Resonance Skill hoặc Resonance Liberation sẽ triệu hồi thêm Chuông Băng khi trúng đích, gây Sát Thương bằng {0} HP tối đa. Cooldown: {1} giây.</t>
+          <t>Khi Resonator đang hoạt động được bảo vệ bởi khiên, Resonance Skill hoặc Resonance Liberation sẽ triệu hồi thêm Chuông Băng khi trúng đích, gây Sát Thương bằng {0} HP tối đa. Thời gian hồi: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -24947,7 +24947,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Nhận Shield sẽ tăng Crit. DMG thêm {0} trong {1} giây.</t>
+          <t>Nhận Khiên sẽ tăng Crit. DMG thêm {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -25012,7 +25012,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Nhận sát thương sẽ tạo khiên tương đương {0} HP tối đa trong {1} giây. Cooldown: {2} giây.</t>
+          <t>Nhận sát thương sẽ tạo khiên tương đương {0} HP tối đa trong {1} giây. Thời gian hồi: {2} giây.</t>
         </is>
       </c>
     </row>
@@ -25077,7 +25077,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Khi được bảo vệ bởi khiên, Tấn Công của Resonator sẽ tăng thêm {0} điểm khiên.</t>
+          <t>Khi được bảo vệ bởi khiên, ATK của Resonator sẽ tăng thêm {0} điểm khiên.</t>
         </is>
       </c>
     </row>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Chuông băng được triệu hồi gây thêm sát thương bằng {0} HP tối đa của Resonator đang kích hoạt.</t>
+          <t>Chuông băng được triệu hồi gây thêm DMG bằng {0} HP tối đa của Resonator đang kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt gây thêm {0} sát thương trong {1} giây sau khi hồi phục.</t>
+          <t>Resonator đang kích hoạt gây thêm {0} DMG trong {1} giây sau khi hồi phục.</t>
         </is>
       </c>
     </row>
@@ -25337,7 +25337,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Attack gây thêm sát thương bằng {0} HP hiện tại một lần. Hồi chiêu: {1} giây.</t>
+          <t>Tấn Công gây thêm DMG bằng {0} HP hiện tại một lần. Thời gian hồi: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -25402,7 +25402,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ tạo khiên cho Resonator đang hoạt động trong {0} giây. Cooldown: {1} giây.</t>
+          <t>Né tránh thành công sẽ tạo khiên cho Resonator đang hoạt động trong {0} giây. Thời gian hồi: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -25857,7 +25857,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Trong vòng {0} giây sau khi sử dụng Resonance Liberation, tăng khả năng chống gián đoạn và giảm {1} sát thương nhận vào.</t>
+          <t>Trong vòng {0} giây sau khi sử dụng Resonance Liberation, tăng khả năng chống gián đoạn và giảm {1} DMG nhận vào.</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>DEF tăng {0}.</t>
+          <t>Phòng Ngự tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -26117,7 +26117,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Giảm {0} Cooldown chiêu Resonance Liberation và {1} Resonance Energy tối đa.</t>
+          <t>Giảm {0} Thời gian hồi chiêu Resonance Liberation và {1} Resonance Energy tối đa.</t>
         </is>
       </c>
     </row>
@@ -26182,7 +26182,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Resonance Skill khi trúng mục tiêu sẽ triệu hồi thêm một Gold Shock, gây sát thương bằng {0} Tấn Công. Hồi chiêu: {1} giây.</t>
+          <t>Resonance Skill khi trúng mục tiêu sẽ triệu hồi thêm một Gold Shock, gây DMG bằng {0} ATK. Thời gian hồi: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -26247,7 +26247,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation lập tức đặt lại Cooldown chiêu Resonance Liberation và hồi toàn bộ Resonance Energy. Cooldown chiêu: {0} giây.</t>
+          <t>Kích hoạt Resonance Liberation lập tức đặt lại Thời gian hồi chiêu Resonance Liberation và hồi toàn bộ Resonance Energy. Thời gian hồi chiêu: {0} giây.</t>
         </is>
       </c>
     </row>
@@ -26312,7 +26312,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Resonance Liberation còn triệu hồi Gold Shock 3 lần khi trúng đích, gây sát thương bằng {0} Tấn Công.</t>
+          <t>Resonance Liberation còn triệu hồi Gold Shock 3 lần khi trúng đích, gây DMG bằng {0} ATK.</t>
         </is>
       </c>
     </row>
@@ -26637,7 +26637,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Mỗi Basic Attack thực hiện sẽ giảm Cooldown chiêu của Resonance Skill và Resonance Liberation đi {0}.</t>
+          <t>Mỗi Đòn Basic Attack thực hiện sẽ giảm Thời gian hồi chiêu của Resonance Skill và Resonance Liberation đi {0}.</t>
         </is>
       </c>
     </row>
@@ -26832,7 +26832,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ giảm Cooldown chiêu của Resonance Skill {0} giây.</t>
+          <t>Kích hoạt Resonance Skill sẽ giảm thời gian hồi chiêu của Resonance Skill {0} giây.</t>
         </is>
       </c>
     </row>
@@ -26897,7 +26897,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Mỗi đòn Basic Attack trúng đích sẽ hồi phục thêm {0} Resonance Energy.</t>
+          <t>Mỗi đòn Đòn Basic Attack trúng đích sẽ hồi phục thêm {0} Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -27092,7 +27092,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Resonance Skill tăng Crit. Rate của Resonator đang kích hoạt thêm {0} trong {1} giây khi trúng đích, tối đa {2} lần cộng dồn.</t>
+          <t>Kỹ năng Cộng Hưởng tăng Crit. Rate của Resonator đang kích hoạt thêm {0} trong {1} giây khi trúng đích, tối đa {2} lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Resonator hiện tại phục hồi {0} điểm Resonance Energy sau khi chịu sát thương hoặc mất HP. Cooldown chiêu: {1} giây.</t>
+          <t>Resonator hiện tại phục hồi {0} điểm Resonance Energy sau khi chịu sát thương hoặc mất HP. Thời gian hồi chiêu: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -27612,7 +27612,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Khi biến thành Hồi Âm, tăng {0} sát thương gây ra và giảm {1} sát thương nhận vào.</t>
+          <t>Khi biến thành Hồi Âm, tăng {0} DMG gây ra và giảm {1} DMG nhận vào.</t>
         </is>
       </c>
     </row>
@@ -27677,7 +27677,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng Kỹ Năng Echo sẽ triệu hồi thêm 3 lần Cơn Gió Đột Kích, gây sát thương bằng {0} Tấn Công. Cooldown: {1} giây.</t>
+          <t>Gây DMG bằng Kỹ Năng Echo sẽ triệu hồi thêm 3 lần Cơn Gió Đột Kích, gây DMG bằng {0} ATK. Thời gian hồi: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -27807,7 +27807,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Skill Khởi Động còn triệu hồi Luồng Gió 5 lần khi trúng mục tiêu, gây Sát Thương bằng {0} Tấn Công. Cooldown chiêu: {1} giây.</t>
+          <t>Kỹ năng Khởi Động còn triệu hồi Luồng Gió 5 lần khi trúng mục tiêu, gây Sát Thương bằng {0} ATK. Thời gian hồi chiêu: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng {1} Sát Thương Kỹ Năng Echo trong {0} giây.</t>
+          <t>Kích hoạt Giải Cứu Cộng Hưởng tăng {1} Sát Thương Kỹ Năng Echo trong {0} giây.</t>
         </is>
       </c>
     </row>
@@ -28002,7 +28002,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Sát thương Intro Skill của Companions Giao Hưởng tăng thêm {0}.</t>
+          <t>DMG Kỹ Năng Khởi Động của Đồng Hành Giao Hưởng tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Cơn Gió Giật hồi phục {0} Concerto Energy khi trúng đích. Cooldown chiêu: {1} giây.</t>
+          <t>Cơn Gió Giật hồi phục {0} Concerto Energy khi trúng đích. Thời gian hồi chiêu: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -28132,7 +28132,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Dodge Counter phục hồi {0} điểm Concerto Energy và giảm {1} giây Cooldown chiêu Kỹ Năng Vọng Âm. Cooldown chiêu: {2} giây.</t>
+          <t>Dodge Counter phục hồi {0} điểm Năng Lượng Giao Hưởng và giảm {1} giây Thời gian hồi chiêu Kỹ Năng Vọng Âm. Thời gian hồi chiêu: {2} giây.</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Giảm Cooldown chiêu Kỹ Năng Echo {0}.</t>
+          <t>Giảm Thời gian hồi chiêu Kỹ Năng Echo {0}.</t>
         </is>
       </c>
     </row>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Bạo kích từ Đồng Hành Concerto tăng Tỷ Lệ Critical Hit và Sát Thương Critical Hit của Resonator chủ động thêm {0} trong {1} giây.</t>
+          <t>Bạo kích từ Đồng Hành Concerto tăng Crit. Rate và Crit. DMG của Resonator chủ động thêm {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -28652,7 +28652,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Tiêu diệt kẻ địch sẽ giảm Cooldown chiêu Kỹ Năng Echo đi {0} giây, kích hoạt mỗi {1} giây một lần.</t>
+          <t>Tiêu diệt kẻ địch sẽ giảm Thời gian hồi chiêu Kỹ Năng Echo đi {0} giây, kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -28717,7 +28717,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Echo sẽ tăng Tấn Công thêm {0} trong {1} giây.</t>
+          <t>Kích hoạt Kỹ Năng Echo sẽ tăng ATK thêm {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -28847,7 +28847,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Echo sẽ tăng Tấn Công thêm {0} trong {1} giây.</t>
+          <t>Kích hoạt Kỹ Năng Echo sẽ tăng ATK thêm {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -28912,7 +28912,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ hồi phục {0} điểm Concerto Energy. Cooldown chiêu: {1} giây.</t>
+          <t>Kích hoạt Resonance Skill sẽ hồi phục {0} điểm Concerto Energy. Thời gian hồi chiêu: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -28977,7 +28977,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation hồi phục {0} Concerto Energy. Cooldown chiêu: {1} giây.</t>
+          <t>Kích hoạt Resonance Liberation hồi phục {0} Concerto Energy. Thời gian hồi chiêu: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -29107,7 +29107,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Khi thành viên trong đội gây &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} Spectro Frazzle, Aero Erosion, Fusion Burst hoặc Havoc Bane lên kẻ địch, họ sẽ gây thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} Chaos. Mỗi lớp Chaos gây sát thương bằng {2} Tấn Công, tối đa {4} lớp. Hiệu ứng này kích hoạt một lần mỗi {3} giây.</t>
+          <t>Khi thành viên trong đội gây &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} Spectro Frazzle, Aero Erosion, Fusion Burst hoặc Havoc Bane lên kẻ địch, họ sẽ gây thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} Chaos. Mỗi lớp Chaos gây DMG bằng {2} ATK, tối đa {4} lớp. Hiệu ứng này kích hoạt một lần mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29172,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Status Tiêu Cực lên kẻ địch sẽ cộng thêm {0} lớp Chaos vào đòn tấn công tiếp theo.</t>
+          <t>Gây Sát Thương Trạng Thái Tiêu Cực lên kẻ địch sẽ cộng thêm {0} lớp Hỗn Loạn vào đòn tấn công tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -29237,7 +29237,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Mỗi khi kẻ địch chịu Sát Thương Status Tiêu Cực, tất cả thành viên trong đội sẽ hồi HP bằng {0} HP tối đa của họ.</t>
+          <t>Mỗi khi kẻ địch chịu Sát Thương Trạng Thái Tiêu Cực, tất cả thành viên trong đội sẽ hồi HP bằng {0} HP tối đa của họ.</t>
         </is>
       </c>
     </row>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Mỗi khi kẻ địch bị nhiễm Spectro Frazzle, Aero Erosion, Fusion Burst hoặc Havoc Bane, chúng sẽ chịu thêm sát thương bằng {0} Tấn Công một lần.</t>
+          <t>Mỗi khi kẻ địch bị nhiễm Spectro Frazzle, Aero Erosion, Fusion Burst hoặc Havoc Bane, chúng sẽ chịu thêm DMG bằng {0} ATK một lần.</t>
         </is>
       </c>
     </row>
@@ -29432,7 +29432,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Mỗi khi kẻ địch chịu Spectro DMG Frazzle, Aero Erosion hoặc Fusion Burst, Resonator đang hoạt động sẽ hồi {0} điểm Resonance Energy.</t>
+          <t>Mỗi khi kẻ địch chịu Sát Thương Spectro Frazzle, Aero Erosion hoặc Fusion Burst, Resonator đang hoạt động sẽ hồi {0} điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -29692,7 +29692,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Mỗi tầng Hỗn Độn làm giảm thêm {0} Tấn Công của kẻ địch.</t>
+          <t>Mỗi tầng Hỗn Độn làm giảm thêm {0} ATK của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -29822,7 +29822,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Resonators bỏ qua {0} Phòng Ngự của kẻ địch.</t>
+          <t>Resonator bỏ qua {0} Phòng Ngự của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -29952,7 +29952,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Mỗi khi kẻ địch chịu Sát Thương Status Tiêu Cực, Resonator đang hoạt động sẽ hồi HP bằng {0} Tấn Công của bản thân, kích hoạt mỗi {1} giây một lần.</t>
+          <t>Mỗi khi kẻ địch chịu Sát Thương Trạng Thái Tiêu Cực, Resonator đang hoạt động sẽ hồi HP bằng {0} ATK của bản thân, kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -30017,7 +30017,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Basic Attack vào kẻ địch bị Hiệu Ứng Havoc sẽ gây thêm sát thương bằng {0} Attack một lần. Cooldown: {1} giây.</t>
+          <t>Basic Attack vào kẻ địch bị Hiệu Ứng Havoc sẽ gây thêm DMG bằng {0} ATK một lần. Hồi Chiêu: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -30082,7 +30082,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch có {0}% khả năng gây 1 tầng Fusion Burst hoặc Havoc Bane cho nó. Cooldown: {1} giây.</t>
+          <t>Gây sát thương lên kẻ địch có {0}% khả năng gây 1 tầng Fusion Burst hoặc Havoc Bane cho nó. Thời gian hồi: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -30147,7 +30147,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch có {0}% khả năng gây 1 tầng Spectro Frazzle hoặc Aero Erosion cho nó. Cooldown: {1} giây.</t>
+          <t>Gây sát thương lên kẻ địch có {0}% khả năng gây 1 tầng Spectro Frazzle hoặc Aero Erosion cho nó. Thời gian hồi: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -30212,7 +30212,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng Kỹ Năng Fusion Burst sẽ giảm thêm {0} Vibration Strength Động.</t>
+          <t>Gây DMG bằng Kỹ Năng Fusion Burst sẽ giảm thêm {0} Độ Rung Động.</t>
         </is>
       </c>
     </row>
@@ -30342,7 +30342,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Spectro Frazzle hoặc Erosion Aero giảm Cooldown chiêu Resonance Skill {0} giây khi gây sát thương. Cooldown chiêu: {1} giây.</t>
+          <t>Rối Loạn Spectro hoặc Xói Mòn Aero giảm Thời gian hồi chiêu Resonance Skill {0} giây khi gây sát thương. Thời gian hồi chiêu: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -30407,7 +30407,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Skill Concerto giảm {0} Phòng Ngự của kẻ địch mang Tật Havoc trong {1} giây khi trúng đòn.</t>
+          <t>Kỹ năng Concerto giảm {0} Phòng Ngự của kẻ địch mang Tật Havoc trong {1} giây khi trúng đòn.</t>
         </is>
       </c>
     </row>
@@ -30472,7 +30472,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Resonators bỏ qua {0} Phòng Ngự của kẻ địch.</t>
+          <t>Resonator bỏ qua {0} Phòng Ngự của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công {0}, Phòng Ngự {1} và HP tối đa {2}.</t>
+          <t>Tăng ATK {0}, Phòng Ngự {1} và HP tối đa {2}.</t>
         </is>
       </c>
     </row>
@@ -30602,7 +30602,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Resonators bỏ qua {0} Phòng Ngự của kẻ địch cho mỗi Havoc đạt được, tối đa {1}.</t>
+          <t>Resonator bỏ qua {0} Phòng Ngự của kẻ địch cho mỗi Havoc đạt được, tối đa {1}.</t>
         </is>
       </c>
     </row>
@@ -30667,7 +30667,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, đồng thời kích hoạt Ngọn Giáo Hổ Phách thêm 4 lần, mỗi lần gây sát thương bằng {0} Tấn Công.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, đồng thời kích hoạt Ngọn Giáo Hổ Phách thêm 4 lần, mỗi lần gây DMG bằng {0} ATK.</t>
         </is>
       </c>
     </row>
@@ -30732,7 +30732,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, ngay lập tức loại bỏ khả năng miễn nhiễm trạng thái Lệch Tune và giảm Phòng Ngự của nó đi {0} trong {1} giây. Cooldown chiêu: {2} giây.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, ngay lập tức loại bỏ khả năng miễn nhiễm trạng thái Lệch Điệu và giảm Phòng Ngự của nó đi {0} trong {1} giây. Thời gian hồi chiêu: {2} giây.</t>
         </is>
       </c>
     </row>
@@ -30797,7 +30797,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, gây hiệu ứng Đứt Tune - Kích Hoạt trong {0} giây. Gây sát thương lên kẻ địch đang bị Đứt Tune - Kích Hoạt sẽ kích hoạt Ngọn Giáo Hổ Phách thêm 2 lần. Cooldown chiêu: {1} giây.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, gây hiệu ứng Đứt Điệu - Kích Hoạt trong {0} giây. Gây sát thương lên kẻ địch đang bị Đứt Điệu - Kích Hoạt sẽ kích hoạt Ngọn Giáo Hổ Phách thêm 2 lần. Thời gian hồi chiêu: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -30863,8 +30863,8 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, gây hiệu ứng Căng Tune - Kích Hoạt trong {0} giây.
-Gây sát thương lên kẻ địch đang bị Căng Tune - Kích Hoạt sẽ tăng thêm Crit. DMG {1}.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, gây hiệu ứng Căng Điệu - Kích Hoạt trong {0} giây.
+Gây DMG lên kẻ địch đang bị Căng Điệu - Kích Hoạt sẽ tăng thêm Crit. DMG {1}.</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Tỷ Lệ deplete Vibration Strength lên {0} và Tấn Công lên {1} trong {2} giây.</t>
+          <t>Kích hoạt Resonance Liberation tăng Tỷ Lệ Giảm Sức Rung lên {0} và ATK lên {1} trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Ngọn Giáo Hổ Phách gây thêm sát thương bằng {0} Tấn Công một lần.</t>
+          <t>Ngọn Giáo Hổ Phách gây thêm DMG bằng {0} ATK một lần.</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, tăng Tấn Công của Resonator đang hoạt động thêm {0} trong {1} giây.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, tăng ATK của Resonator đang hoạt động thêm {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Kẻ địch bị Hóa Bất Động chịu thêm {0} sát thương.</t>
+          <t>Kẻ địch bị Hóa Bất Động chịu thêm {0} DMG.</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Tấn Công kẻ địch Bất Động sẽ kích hoạt sát thương bổ sung bằng {0} Tấn Công. Cooldown: {1} giây.</t>
+          <t>ATK kẻ địch Bất Động sẽ kích hoạt DMG bổ sung bằng {0} ATK. Thời gian hồi: {1} giây.</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Skill Phá Âm sẽ khôi phục {0} điểm Resonance Energy.</t>
+          <t>Kỹ năng Phá Âm sẽ khôi phục {0} điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, phục hồi HP bằng {0} HP tối đa.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, phục hồi HP bằng {0} HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch sẽ tăng thêm Mức Độ Mất Nhịp của chúng. Cooldown: {0} giây.</t>
+          <t>Gây sát thương lên kẻ địch sẽ tăng thêm Mức Độ Mất Nhịp của chúng. Thời gian hồi: {0} giây.</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Tăng Off-Tune Level của kẻ địch sẽ gia tăng Tấn Công thêm {0} trong {1} giây, có thể chồng chất lên đến {2} lần.</t>
+          <t>Tăng Mức Lệch Tần của kẻ địch sẽ gia tăng ATK thêm {0} trong {1} giây, có thể chồng chất lên đến {2} lần.</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Tăng Off-Tune Level của kẻ địch sẽ gia tăng Phòng Ngự thêm {0} trong {1} giây, có thể chồng chất lên đến {2} lần.</t>
+          <t>Tăng Mức Lệch Tần của kẻ địch sẽ gia tăng Phòng Ngự thêm {0} trong {1} giây, có thể chồng chất lên đến {2} lần.</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Tỷ lệ deplete Vibration Strength của Companions Giao Hưởng tăng thêm {0}.</t>
+          <t>Tỷ lệ Giảm Sức Rung của Đồng Hành Giao Hưởng tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Không nhận sát thương trong chiến đấu sẽ tăng Crit. DMG.</t>
+          <t>Không nhận DMG trong chiến đấu sẽ tăng Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Các đòn tấn công liên tiếp gia tăng Tấn Công và Phòng Ngự.</t>
+          <t>Các đòn tấn công liên tiếp gia tăng ATK và Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Đòn đánh liên tiếp tăng Crit. Rate.</t>
+          <t>Các đòn tấn công liên tiếp gia tăng Crit. Rate.</t>
         </is>
       </c>
     </row>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Đòn đánh liên tiếp phục hồi HP.</t>
+          <t>Các đòn tấn công liên tiếp hồi phục HP.</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Tăng DMG Basic Attack.</t>
+          <t>Tăng Sát Thương Kỹ Năng Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Critical Hit tăng Sát Thương Heavy Attack.</t>
+          <t>Bạo Kích tăng Sát Thương Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Mỗi Fusion nhận được tăng ATK.</t>
+          <t>Mỗi Fusion thu thập được tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -32749,7 +32749,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Critical Hit tăng Tấn Công.</t>
+          <t>Bạo Kích tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Dodge thành công tăng Crit. Rate của Resonator đang hoạt động.</t>
+          <t>Né tránh thành công tăng Crit. Rate của Resonator đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Heavy Attack tăng Crit. DMG khi trúng mục tiêu.</t>
+          <t>Đòn Heavy Attack tăng Crit. DMG khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Tăng DMG Basic Attack.</t>
+          <t>Tăng Sát Thương Kỹ Năng Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -33139,7 +33139,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Tăng Sát Thương Heavy Attack.</t>
+          <t>Tăng Sát Thương Đòn Heavy Attack.</t>
         </is>
       </c>
     </row>
@@ -33204,7 +33204,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Resonance Skill trúng đích tăng Sát Thương.</t>
+          <t>Kỹ năng Cộng Hưởng trúng đích tăng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -33269,7 +33269,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Khi Resonator đang hoạt động được bảo vệ bởi khiên, Basic Attack hoặc Nặng sẽ triệu hồi Chuông Băng khi trúng đích.</t>
+          <t>Khi Resonator đang hoạt động được bảo vệ bởi khiên, Đòn Tấn Công Cơ Bản hoặc Nặng sẽ triệu hồi Chuông Băng khi trúng đích.</t>
         </is>
       </c>
     </row>
